--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -855,37 +855,37 @@
         <v>20</v>
       </c>
       <c r="D14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="15">
         <v>-100</v>
       </c>
-      <c r="F14" s="14">
-        <v>2</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
       </c>
       <c r="J14" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K14" s="15">
-        <v>-60</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L14" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="M14" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N14" s="15">
-        <v>-96.363636363636</v>
+        <v>-96.721311475409</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" s="15">
-        <v>-40</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F15" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G15" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H15" s="15">
-        <v>21.052631578947</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="J15" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K15" s="15">
-        <v>-9.677419354838</v>
+        <v>10.810810810810</v>
       </c>
       <c r="L15" s="15">
-        <v>86.666666666666</v>
+        <v>115.789473684211</v>
       </c>
       <c r="M15" s="15">
-        <v>16.666666666666</v>
+        <v>51.851851851851</v>
       </c>
       <c r="N15" s="15">
-        <v>-51.724137931034</v>
+        <v>-44.594594594594</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="14">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E16" s="15">
-        <v>25.925925925925</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="F16" s="14">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G16" s="14">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="H16" s="15">
-        <v>16.071428571428</v>
+        <v>3.053435114503</v>
       </c>
       <c r="I16" s="14">
-        <v>196</v>
+        <v>237</v>
       </c>
       <c r="J16" s="14">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="K16" s="15">
-        <v>24.050632911392</v>
+        <v>19.095477386934</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.904214559387</v>
+        <v>-22.801302931596</v>
       </c>
       <c r="M16" s="15">
-        <v>-46.883468834688</v>
+        <v>-41.911764705882</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.850967007963</v>
+        <v>-88.370951913640</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D17" s="14">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E17" s="15">
-        <v>-40.909090909090</v>
+        <v>-1.315789473684</v>
       </c>
       <c r="F17" s="14">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G17" s="14">
         <v>282</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.546099290780</v>
+        <v>-5.673758865248</v>
       </c>
       <c r="I17" s="14">
-        <v>394</v>
+        <v>475</v>
       </c>
       <c r="J17" s="14">
-        <v>390</v>
+        <v>466</v>
       </c>
       <c r="K17" s="15">
-        <v>1.025641025641</v>
+        <v>1.931330472103</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.955665024630</v>
+        <v>-3.258655804480</v>
       </c>
       <c r="M17" s="15">
-        <v>34.470989761092</v>
+        <v>36.103151862464</v>
       </c>
       <c r="N17" s="15">
-        <v>-50.75</v>
+        <v>-48.593073593073</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D18" s="14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E18" s="15">
-        <v>-3.846153846153</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="F18" s="14">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G18" s="14">
         <v>129</v>
       </c>
       <c r="H18" s="15">
-        <v>-6.201550387596</v>
+        <v>-4.651162790697</v>
       </c>
       <c r="I18" s="14">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="J18" s="14">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="K18" s="15">
-        <v>-5.617977528089</v>
+        <v>-0.473933649289</v>
       </c>
       <c r="L18" s="15">
-        <v>-28.205128205128</v>
+        <v>-19.847328244274</v>
       </c>
       <c r="M18" s="15">
-        <v>-42.068965517241</v>
+        <v>-37.125748502994</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.653287788215</v>
+        <v>-84.478935698447</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D19" s="14">
         <v>85</v>
       </c>
       <c r="E19" s="15">
-        <v>7.058823529411</v>
+        <v>3.529411764705</v>
       </c>
       <c r="F19" s="14">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="G19" s="14">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="H19" s="15">
-        <v>4.491017964071</v>
+        <v>-3.206997084548</v>
       </c>
       <c r="I19" s="14">
-        <v>482</v>
+        <v>570</v>
       </c>
       <c r="J19" s="14">
-        <v>455</v>
+        <v>540</v>
       </c>
       <c r="K19" s="15">
-        <v>5.934065934065</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L19" s="15">
-        <v>-9.737827715355</v>
+        <v>-9.379968203497</v>
       </c>
       <c r="M19" s="15">
-        <v>35.393258426966</v>
+        <v>35.391923990498</v>
       </c>
       <c r="N19" s="15">
-        <v>-23.854660347551</v>
+        <v>-21.487603305785</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D20" s="14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E20" s="15">
-        <v>27.777777777777</v>
+        <v>-12</v>
       </c>
       <c r="F20" s="14">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G20" s="14">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H20" s="15">
-        <v>25</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I20" s="14">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="J20" s="14">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="K20" s="15">
-        <v>13.636363636363</v>
+        <v>6.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-32.065217391304</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="M20" s="15">
-        <v>-2.34375</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.372093023255</v>
+        <v>-88.723570869224</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="D21" s="17">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="E21" s="18">
-        <v>-8.8</v>
+        <v>-0.746268656716</v>
       </c>
       <c r="F21" s="17">
-        <v>987</v>
+        <v>968</v>
       </c>
       <c r="G21" s="17">
-        <v>952</v>
+        <v>989</v>
       </c>
       <c r="H21" s="18">
-        <v>3.676470588235</v>
+        <v>-2.123356926188</v>
       </c>
       <c r="I21" s="17">
-        <v>1395</v>
+        <v>1679</v>
       </c>
       <c r="J21" s="17">
-        <v>1327</v>
+        <v>1595</v>
       </c>
       <c r="K21" s="18">
-        <v>5.124340617935</v>
+        <v>5.266457680250</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.990859232175</v>
+        <v>-12.688507540301</v>
       </c>
       <c r="M21" s="18">
-        <v>-4.972752043596</v>
+        <v>-1.235294117647</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.864864864864</v>
+        <v>-73.981094064776</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D22" s="14">
         <v>9</v>
       </c>
       <c r="E22" s="15">
-        <v>-11.111111111111</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F22" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G22" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H22" s="15">
-        <v>-25.925925925925</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I22" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J22" s="14">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K22" s="15">
-        <v>-8.108108108108</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="L22" s="15">
-        <v>-27.659574468085</v>
+        <v>-25</v>
       </c>
       <c r="M22" s="15">
-        <v>-20.930232558139</v>
+        <v>-20.408163265306</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>29</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D23" s="14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E23" s="15">
-        <v>-59.375</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F23" s="14">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G23" s="14">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H23" s="15">
-        <v>-15.841584158415</v>
+        <v>-12.149532710280</v>
       </c>
       <c r="I23" s="14">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="J23" s="14">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="K23" s="15">
-        <v>-16.783216783216</v>
+        <v>-9.467455621301</v>
       </c>
       <c r="L23" s="15">
-        <v>-17.931034482758</v>
+        <v>-13.068181818181</v>
       </c>
       <c r="M23" s="15">
-        <v>21.428571428571</v>
+        <v>37.837837837837</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>29</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D24" s="14">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="E24" s="15">
-        <v>9.523809523809</v>
+        <v>3.448275862068</v>
       </c>
       <c r="F24" s="14">
-        <v>848</v>
+        <v>834</v>
       </c>
       <c r="G24" s="14">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="H24" s="15">
-        <v>3.163017031630</v>
+        <v>1.707317073170</v>
       </c>
       <c r="I24" s="14">
-        <v>1165</v>
+        <v>1375</v>
       </c>
       <c r="J24" s="14">
-        <v>1131</v>
+        <v>1334</v>
       </c>
       <c r="K24" s="15">
-        <v>3.006189213085</v>
+        <v>3.073463268365</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.559602649006</v>
+        <v>-5.950752393980</v>
       </c>
       <c r="M24" s="15">
-        <v>16.151545363908</v>
+        <v>20.614035087719</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>29</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D25" s="14">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E25" s="15">
-        <v>23.880597014925</v>
+        <v>12.5</v>
       </c>
       <c r="F25" s="14">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G25" s="14">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="H25" s="15">
-        <v>2.684563758389</v>
+        <v>0.645161290322</v>
       </c>
       <c r="I25" s="14">
-        <v>423</v>
+        <v>501</v>
       </c>
       <c r="J25" s="14">
-        <v>423</v>
+        <v>495</v>
       </c>
       <c r="K25" s="15">
-        <v>0</v>
+        <v>1.212121212121</v>
       </c>
       <c r="L25" s="15">
-        <v>-13.141683778234</v>
+        <v>-17.190082644628</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>29</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D26" s="14">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E26" s="15">
-        <v>27.184466019417</v>
+        <v>4.310344827586</v>
       </c>
       <c r="F26" s="14">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="G26" s="14">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H26" s="15">
-        <v>8.793969849246</v>
+        <v>14.646464646464</v>
       </c>
       <c r="I26" s="14">
-        <v>579</v>
+        <v>703</v>
       </c>
       <c r="J26" s="14">
-        <v>535</v>
+        <v>651</v>
       </c>
       <c r="K26" s="15">
-        <v>8.224299065420</v>
+        <v>7.987711213517</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.763285024154</v>
+        <v>-3.168044077134</v>
       </c>
       <c r="M26" s="15">
-        <v>-20.357634112792</v>
+        <v>-17.294117647058</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>29</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27" s="15">
-        <v>-40</v>
+        <v>85.714285714285</v>
       </c>
       <c r="F27" s="14">
+        <v>30</v>
+      </c>
+      <c r="G27" s="14">
         <v>25</v>
       </c>
-      <c r="G27" s="14">
-        <v>26</v>
-      </c>
       <c r="H27" s="15">
-        <v>-3.846153846153</v>
+        <v>20</v>
       </c>
       <c r="I27" s="14">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="J27" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K27" s="15">
-        <v>-23.076923076923</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>29</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D28" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E28" s="15">
-        <v>28.571428571428</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F28" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G28" s="14">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>-10.869565217391</v>
       </c>
       <c r="I28" s="14">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="J28" s="14">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K28" s="15">
-        <v>-13.235294117647</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="L28" s="15">
-        <v>25.531914893617</v>
+        <v>21.052631578947</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>29</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>4</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-75</v>
+      </c>
+      <c r="F29" s="14">
+        <v>5</v>
+      </c>
+      <c r="G29" s="14">
+        <v>11</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-54.545454545454</v>
+      </c>
+      <c r="I29" s="14">
+        <v>11</v>
+      </c>
+      <c r="J29" s="14">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="14">
-        <v>7</v>
-      </c>
-      <c r="G29" s="14">
-        <v>10</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-30</v>
-      </c>
-      <c r="I29" s="14">
-        <v>10</v>
-      </c>
-      <c r="J29" s="14">
-        <v>16</v>
-      </c>
       <c r="K29" s="15">
-        <v>-37.5</v>
+        <v>-45</v>
       </c>
       <c r="L29" s="15">
-        <v>-47.368421052631</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="M29" s="15">
-        <v>-71.428571428571</v>
+        <v>-70.270270270270</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.049504950495</v>
+        <v>-95.022624434389</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F30" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="14">
+        <v>11</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-63.636363636363</v>
+      </c>
+      <c r="I30" s="14">
         <v>9</v>
       </c>
-      <c r="H30" s="15">
-        <v>-44.444444444444</v>
-      </c>
-      <c r="I30" s="14">
-        <v>8</v>
-      </c>
       <c r="J30" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K30" s="15">
-        <v>-38.461538461538</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="L30" s="15">
-        <v>-52.941176470588</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="M30" s="15">
-        <v>-73.333333333333</v>
+        <v>-70.967741935483</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.789473684210</v>
+        <v>-95.693779904306</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,25 +1558,25 @@
         <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" s="15">
-        <v>75</v>
+        <v>-20</v>
       </c>
       <c r="I31" s="14">
         <v>8</v>
       </c>
       <c r="J31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L31" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>29</v>
@@ -1617,13 +1617,13 @@
         <v>29</v>
       </c>
       <c r="F33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
         <v>3</v>

--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -199,61 +199,61 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,738 +851,738 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="14">
         <v>2</v>
       </c>
       <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+        <v>-50</v>
+      </c>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K14" s="15">
-        <v>-71.428571428571</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-75</v>
+        <v>-70</v>
       </c>
       <c r="M14" s="15">
-        <v>-77.777777777777</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="N14" s="15">
-        <v>-96.721311475409</v>
+        <v>-95.522388059701</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D15" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>116.666666666667</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F15" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G15" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H15" s="15">
-        <v>33.333333333333</v>
+        <v>81.25</v>
       </c>
       <c r="I15" s="14">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="J15" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K15" s="15">
-        <v>10.810810810810</v>
+        <v>27.5</v>
       </c>
       <c r="L15" s="15">
-        <v>115.789473684211</v>
+        <v>131.818181818182</v>
       </c>
       <c r="M15" s="15">
-        <v>51.851851851851</v>
+        <v>82.142857142857</v>
       </c>
       <c r="N15" s="15">
-        <v>-44.594594594594</v>
+        <v>-39.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
         <v>36</v>
       </c>
       <c r="D16" s="14">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E16" s="15">
-        <v>-12.195121951219</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F16" s="14">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G16" s="14">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H16" s="15">
-        <v>3.053435114503</v>
+        <v>9.022556390977</v>
       </c>
       <c r="I16" s="14">
-        <v>237</v>
+        <v>276</v>
       </c>
       <c r="J16" s="14">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="K16" s="15">
-        <v>19.095477386934</v>
+        <v>21.585903083700</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.801302931596</v>
+        <v>-21.813031161473</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.911764705882</v>
+        <v>-37.556561085972</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.370951913640</v>
+        <v>-87.942332896461</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D17" s="14">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E17" s="15">
-        <v>-1.315789473684</v>
+        <v>-26.190476190476</v>
       </c>
       <c r="F17" s="14">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="G17" s="14">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="H17" s="15">
-        <v>-5.673758865248</v>
+        <v>-15.771812080536</v>
       </c>
       <c r="I17" s="14">
-        <v>475</v>
+        <v>540</v>
       </c>
       <c r="J17" s="14">
-        <v>466</v>
+        <v>550</v>
       </c>
       <c r="K17" s="15">
-        <v>1.931330472103</v>
+        <v>-1.818181818181</v>
       </c>
       <c r="L17" s="15">
-        <v>-3.258655804480</v>
+        <v>-2.350813743218</v>
       </c>
       <c r="M17" s="15">
-        <v>36.103151862464</v>
+        <v>33.004926108374</v>
       </c>
       <c r="N17" s="15">
-        <v>-48.593073593073</v>
+        <v>-48.669201520912</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D18" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E18" s="15">
-        <v>-3.030303030303</v>
+        <v>8.571428571428</v>
       </c>
       <c r="F18" s="14">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="G18" s="14">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H18" s="15">
-        <v>-4.651162790697</v>
+        <v>11.2</v>
       </c>
       <c r="I18" s="14">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="J18" s="14">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="K18" s="15">
-        <v>-0.473933649289</v>
+        <v>2.439024390243</v>
       </c>
       <c r="L18" s="15">
-        <v>-19.847328244274</v>
+        <v>-13.402061855670</v>
       </c>
       <c r="M18" s="15">
-        <v>-37.125748502994</v>
+        <v>-31.707317073170</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.478935698447</v>
+        <v>-83.783783783783</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D19" s="14">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E19" s="15">
-        <v>3.529411764705</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F19" s="14">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="G19" s="14">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="H19" s="15">
-        <v>-3.206997084548</v>
+        <v>-6.629834254143</v>
       </c>
       <c r="I19" s="14">
-        <v>570</v>
+        <v>660</v>
       </c>
       <c r="J19" s="14">
-        <v>540</v>
+        <v>635</v>
       </c>
       <c r="K19" s="15">
-        <v>5.555555555555</v>
+        <v>3.937007874015</v>
       </c>
       <c r="L19" s="15">
-        <v>-9.379968203497</v>
+        <v>-10.326086956521</v>
       </c>
       <c r="M19" s="15">
-        <v>35.391923990498</v>
+        <v>34.419551934826</v>
       </c>
       <c r="N19" s="15">
-        <v>-21.487603305785</v>
+        <v>-19.018404907975</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>25</v>
       </c>
       <c r="E20" s="15">
-        <v>-12</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G20" s="14">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H20" s="15">
-        <v>7.692307692307</v>
+        <v>-5.813953488372</v>
       </c>
       <c r="I20" s="14">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="J20" s="14">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="K20" s="15">
-        <v>6.666666666666</v>
+        <v>3.125</v>
       </c>
       <c r="L20" s="15">
-        <v>-30.434782608695</v>
+        <v>-28.879310344827</v>
       </c>
       <c r="M20" s="15">
-        <v>-5.263157894736</v>
+        <v>-8.839779005524</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.723570869224</v>
+        <v>-88.783140720598</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="D21" s="17">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E21" s="18">
-        <v>-0.746268656716</v>
+        <v>-6.25</v>
       </c>
       <c r="F21" s="17">
-        <v>968</v>
+        <v>984</v>
       </c>
       <c r="G21" s="17">
-        <v>989</v>
+        <v>1026</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.123356926188</v>
+        <v>-4.093567251461</v>
       </c>
       <c r="I21" s="17">
-        <v>1679</v>
+        <v>1947</v>
       </c>
       <c r="J21" s="17">
-        <v>1595</v>
+        <v>1867</v>
       </c>
       <c r="K21" s="18">
-        <v>5.266457680250</v>
+        <v>4.284949116229</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.688507540301</v>
+        <v>-11.379153390987</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.235294117647</v>
+        <v>0.828586224754</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.981094064776</v>
+        <v>-73.445171849427</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="14">
+        <v>10</v>
+      </c>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>400</v>
+      </c>
+      <c r="F22" s="14">
+        <v>30</v>
+      </c>
+      <c r="G22" s="14">
+        <v>27</v>
+      </c>
+      <c r="H22" s="15">
+        <v>11.111111111111</v>
+      </c>
+      <c r="I22" s="14">
+        <v>49</v>
+      </c>
+      <c r="J22" s="14">
+        <v>48</v>
+      </c>
+      <c r="K22" s="15">
+        <v>2.083333333333</v>
+      </c>
+      <c r="L22" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="M22" s="15">
+        <v>-18.333333333333</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="C22" s="14">
-        <v>6</v>
-      </c>
-      <c r="D22" s="14">
-        <v>9</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F22" s="14">
-        <v>24</v>
-      </c>
-      <c r="G22" s="14">
-        <v>28</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="I22" s="14">
-        <v>39</v>
-      </c>
-      <c r="J22" s="14">
-        <v>46</v>
-      </c>
-      <c r="K22" s="15">
-        <v>-15.217391304347</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-25</v>
-      </c>
-      <c r="M22" s="15">
-        <v>-20.408163265306</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D23" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E23" s="15">
-        <v>23.076923076923</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="F23" s="14">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G23" s="14">
         <v>107</v>
       </c>
       <c r="H23" s="15">
-        <v>-12.149532710280</v>
+        <v>-15.887850467289</v>
       </c>
       <c r="I23" s="14">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="J23" s="14">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="K23" s="15">
-        <v>-9.467455621301</v>
+        <v>-9.183673469387</v>
       </c>
       <c r="L23" s="15">
-        <v>-13.068181818181</v>
+        <v>-12.315270935960</v>
       </c>
       <c r="M23" s="15">
-        <v>37.837837837837</v>
+        <v>42.4</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D24" s="14">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="E24" s="15">
-        <v>3.448275862068</v>
+        <v>13.612565445026</v>
       </c>
       <c r="F24" s="14">
-        <v>834</v>
+        <v>795</v>
       </c>
       <c r="G24" s="14">
-        <v>820</v>
+        <v>789</v>
       </c>
       <c r="H24" s="15">
-        <v>1.707317073170</v>
+        <v>0.760456273764</v>
       </c>
       <c r="I24" s="14">
-        <v>1375</v>
+        <v>1587</v>
       </c>
       <c r="J24" s="14">
-        <v>1334</v>
+        <v>1525</v>
       </c>
       <c r="K24" s="15">
-        <v>3.073463268365</v>
+        <v>4.065573770491</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.950752393980</v>
+        <v>-6.094674556213</v>
       </c>
       <c r="M24" s="15">
-        <v>20.614035087719</v>
+        <v>23.405909797822</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D25" s="14">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="E25" s="15">
-        <v>12.5</v>
+        <v>-27.884615384615</v>
       </c>
       <c r="F25" s="14">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="G25" s="14">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="H25" s="15">
-        <v>0.645161290322</v>
+        <v>-7.598784194528</v>
       </c>
       <c r="I25" s="14">
-        <v>501</v>
+        <v>575</v>
       </c>
       <c r="J25" s="14">
-        <v>495</v>
+        <v>599</v>
       </c>
       <c r="K25" s="15">
-        <v>1.212121212121</v>
+        <v>-4.006677796327</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.190082644628</v>
+        <v>-19.804741980474</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D26" s="14">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="E26" s="15">
-        <v>4.310344827586</v>
+        <v>27</v>
       </c>
       <c r="F26" s="14">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="G26" s="14">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H26" s="15">
-        <v>14.646464646464</v>
+        <v>17.690417690417</v>
       </c>
       <c r="I26" s="14">
-        <v>703</v>
+        <v>828</v>
       </c>
       <c r="J26" s="14">
-        <v>651</v>
+        <v>751</v>
       </c>
       <c r="K26" s="15">
-        <v>7.987711213517</v>
+        <v>10.252996005326</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.168044077134</v>
+        <v>1.098901098901</v>
       </c>
       <c r="M26" s="15">
-        <v>-17.294117647058</v>
+        <v>-15.163934426229</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D27" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>85.714285714285</v>
+        <v>233.333333333333</v>
       </c>
       <c r="F27" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G27" s="14">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H27" s="15">
-        <v>20</v>
+        <v>72.222222222222</v>
       </c>
       <c r="I27" s="14">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="J27" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K27" s="15">
-        <v>-4.347826086956</v>
+        <v>12.244897959183</v>
       </c>
       <c r="L27" s="15">
-        <v>4.761904761904</v>
+        <v>19.565217391304</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E28" s="15">
-        <v>-15.384615384615</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G28" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H28" s="15">
-        <v>-10.869565217391</v>
+        <v>-2.083333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="J28" s="14">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K28" s="15">
-        <v>-14.814814814814</v>
+        <v>-7.526881720430</v>
       </c>
       <c r="L28" s="15">
-        <v>21.052631578947</v>
+        <v>26.470588235294</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>-75</v>
+        <v>100</v>
       </c>
       <c r="F29" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G29" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H29" s="15">
-        <v>-54.545454545454</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I29" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J29" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K29" s="15">
-        <v>-45</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="L29" s="15">
-        <v>-47.619047619047</v>
+        <v>-37.5</v>
       </c>
       <c r="M29" s="15">
-        <v>-70.270270270270</v>
+        <v>-67.391304347826</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.022624434389</v>
+        <v>-94.140625</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30" s="15">
-        <v>-75</v>
+        <v>50</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H30" s="15">
-        <v>-63.636363636363</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I30" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J30" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K30" s="15">
-        <v>-47.058823529411</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="L30" s="15">
-        <v>-52.631578947368</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M30" s="15">
-        <v>-70.967741935483</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.693779904306</v>
+        <v>-95.081967213114</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="14">
+        <v>2</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="E31" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="F31" s="14">
         <v>4</v>
       </c>
       <c r="G31" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H31" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J31" s="14">
         <v>5</v>
       </c>
       <c r="K31" s="15">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,40 +1608,40 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="L33" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>708</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>20509</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>9978</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>14993</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>8788</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>12552</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>68033</v>

--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -861,31 +861,31 @@
         <v>-50</v>
       </c>
       <c r="F14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" s="15">
-        <v>-83.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K14" s="15">
-        <v>-66.666666666666</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L14" s="15">
-        <v>-70</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="M14" s="15">
-        <v>-78.571428571428</v>
+        <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-95.522388059701</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" s="15">
-        <v>166.666666666667</v>
+        <v>80</v>
       </c>
       <c r="F15" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G15" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H15" s="15">
-        <v>81.25</v>
+        <v>73.684210526315</v>
       </c>
       <c r="I15" s="14">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="J15" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K15" s="15">
-        <v>27.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>131.818181818182</v>
+        <v>130.769230769231</v>
       </c>
       <c r="M15" s="15">
-        <v>82.142857142857</v>
+        <v>57.894736842105</v>
       </c>
       <c r="N15" s="15">
-        <v>-39.285714285714</v>
+        <v>-38.144329896907</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D16" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" s="15">
-        <v>28.571428571428</v>
+        <v>14.814814814814</v>
       </c>
       <c r="F16" s="14">
         <v>145</v>
       </c>
       <c r="G16" s="14">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="H16" s="15">
-        <v>9.022556390977</v>
+        <v>17.886178861788</v>
       </c>
       <c r="I16" s="14">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="J16" s="14">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="K16" s="15">
-        <v>21.585903083700</v>
+        <v>21.259842519685</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.813031161473</v>
+        <v>-24.694376528117</v>
       </c>
       <c r="M16" s="15">
-        <v>-37.556561085972</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.942332896461</v>
+        <v>-88.085106382978</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D17" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E17" s="15">
-        <v>-26.190476190476</v>
+        <v>-17.582417582417</v>
       </c>
       <c r="F17" s="14">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="G17" s="14">
-        <v>298</v>
+        <v>339</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.771812080536</v>
+        <v>-19.174041297935</v>
       </c>
       <c r="I17" s="14">
-        <v>540</v>
+        <v>623</v>
       </c>
       <c r="J17" s="14">
-        <v>550</v>
+        <v>641</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.818181818181</v>
+        <v>-2.808112324492</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.350813743218</v>
+        <v>-1.579778830963</v>
       </c>
       <c r="M17" s="15">
-        <v>33.004926108374</v>
+        <v>39.686098654708</v>
       </c>
       <c r="N17" s="15">
-        <v>-48.669201520912</v>
+        <v>-47.381756756756</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D18" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E18" s="15">
-        <v>8.571428571428</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="F18" s="14">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G18" s="14">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H18" s="15">
-        <v>11.2</v>
+        <v>4.580152671755</v>
       </c>
       <c r="I18" s="14">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="J18" s="14">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="K18" s="15">
-        <v>2.439024390243</v>
+        <v>2.473498233215</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.402061855670</v>
+        <v>-9.375</v>
       </c>
       <c r="M18" s="15">
-        <v>-31.707317073170</v>
+        <v>-31.116389548693</v>
       </c>
       <c r="N18" s="15">
-        <v>-83.783783783783</v>
+        <v>-83.409610983981</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D19" s="14">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="E19" s="15">
-        <v>-5.263157894736</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="F19" s="14">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G19" s="14">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.629834254143</v>
+        <v>-11.405835543766</v>
       </c>
       <c r="I19" s="14">
-        <v>660</v>
+        <v>730</v>
       </c>
       <c r="J19" s="14">
-        <v>635</v>
+        <v>747</v>
       </c>
       <c r="K19" s="15">
-        <v>3.937007874015</v>
+        <v>-2.275769745649</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.326086956521</v>
+        <v>-14.419695193434</v>
       </c>
       <c r="M19" s="15">
-        <v>34.419551934826</v>
+        <v>30.590339892665</v>
       </c>
       <c r="N19" s="15">
-        <v>-19.018404907975</v>
+        <v>-20.995670995671</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D20" s="14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E20" s="15">
-        <v>-20</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F20" s="14">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G20" s="14">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="H20" s="15">
-        <v>-5.813953488372</v>
+        <v>-16.831683168316</v>
       </c>
       <c r="I20" s="14">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="J20" s="14">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="K20" s="15">
-        <v>3.125</v>
+        <v>-4.663212435233</v>
       </c>
       <c r="L20" s="15">
-        <v>-28.879310344827</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="M20" s="15">
-        <v>-8.839779005524</v>
+        <v>-8.457711442786</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.783140720598</v>
+        <v>-89.014925373134</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D21" s="17">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="E21" s="18">
-        <v>-6.25</v>
+        <v>-20.846905537459</v>
       </c>
       <c r="F21" s="17">
-        <v>984</v>
+        <v>1009</v>
       </c>
       <c r="G21" s="17">
-        <v>1026</v>
+        <v>1097</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.093567251461</v>
+        <v>-8.021877848678</v>
       </c>
       <c r="I21" s="17">
-        <v>1947</v>
+        <v>2199</v>
       </c>
       <c r="J21" s="17">
-        <v>1867</v>
+        <v>2174</v>
       </c>
       <c r="K21" s="18">
-        <v>4.284949116229</v>
+        <v>1.149954001839</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.379153390987</v>
+        <v>-12.668784749801</v>
       </c>
       <c r="M21" s="18">
-        <v>0.828586224754</v>
+        <v>1.056985294117</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.445171849427</v>
+        <v>-73.470865001809</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>400</v>
+        <v>75</v>
       </c>
       <c r="F22" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G22" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H22" s="15">
-        <v>11.111111111111</v>
+        <v>29.166666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J22" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K22" s="15">
-        <v>2.083333333333</v>
+        <v>5.769230769230</v>
       </c>
       <c r="L22" s="15">
-        <v>-12.5</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M22" s="15">
-        <v>-18.333333333333</v>
+        <v>-20.289855072463</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>28</v>
@@ -1221,37 +1221,37 @@
         <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D23" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E23" s="15">
-        <v>-14.814814814814</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="F23" s="14">
         <v>90</v>
       </c>
       <c r="G23" s="14">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="H23" s="15">
-        <v>-15.887850467289</v>
+        <v>-24.369747899159</v>
       </c>
       <c r="I23" s="14">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="J23" s="14">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="K23" s="15">
-        <v>-9.183673469387</v>
+        <v>-14.347826086956</v>
       </c>
       <c r="L23" s="15">
-        <v>-12.315270935960</v>
+        <v>-15.450643776824</v>
       </c>
       <c r="M23" s="15">
-        <v>42.4</v>
+        <v>35.862068965517</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>28</v>
@@ -1262,37 +1262,37 @@
         <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="D24" s="14">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="E24" s="15">
-        <v>13.612565445026</v>
+        <v>-13.063063063063</v>
       </c>
       <c r="F24" s="14">
-        <v>795</v>
+        <v>827</v>
       </c>
       <c r="G24" s="14">
-        <v>789</v>
+        <v>805</v>
       </c>
       <c r="H24" s="15">
-        <v>0.760456273764</v>
+        <v>2.732919254658</v>
       </c>
       <c r="I24" s="14">
-        <v>1587</v>
+        <v>1778</v>
       </c>
       <c r="J24" s="14">
-        <v>1525</v>
+        <v>1747</v>
       </c>
       <c r="K24" s="15">
-        <v>4.065573770491</v>
+        <v>1.774470520892</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.094674556213</v>
+        <v>-10.337871911245</v>
       </c>
       <c r="M24" s="15">
-        <v>23.405909797822</v>
+        <v>24.335664335664</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>28</v>
@@ -1303,34 +1303,34 @@
         <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D25" s="14">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E25" s="15">
-        <v>-27.884615384615</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="F25" s="14">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G25" s="14">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.598784194528</v>
+        <v>-9.467455621301</v>
       </c>
       <c r="I25" s="14">
-        <v>575</v>
+        <v>644</v>
       </c>
       <c r="J25" s="14">
-        <v>599</v>
+        <v>694</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.006677796327</v>
+        <v>-7.204610951008</v>
       </c>
       <c r="L25" s="15">
-        <v>-19.804741980474</v>
+        <v>-25.203252032520</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>28</v>
@@ -1344,37 +1344,37 @@
         <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="D26" s="14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E26" s="15">
-        <v>27</v>
+        <v>-15.454545454545</v>
       </c>
       <c r="F26" s="14">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="G26" s="14">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="H26" s="15">
-        <v>17.690417690417</v>
+        <v>8.624708624708</v>
       </c>
       <c r="I26" s="14">
-        <v>828</v>
+        <v>912</v>
       </c>
       <c r="J26" s="14">
-        <v>751</v>
+        <v>861</v>
       </c>
       <c r="K26" s="15">
-        <v>10.252996005326</v>
+        <v>5.923344947735</v>
       </c>
       <c r="L26" s="15">
-        <v>1.098901098901</v>
+        <v>-4.201680672268</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.163934426229</v>
+        <v>-17.316409791477</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>28</v>
@@ -1388,31 +1388,31 @@
         <v>10</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E27" s="15">
-        <v>233.333333333333</v>
+        <v>25</v>
       </c>
       <c r="F27" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G27" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H27" s="15">
-        <v>72.222222222222</v>
+        <v>56.521739130434</v>
       </c>
       <c r="I27" s="14">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J27" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K27" s="15">
-        <v>12.244897959183</v>
+        <v>14.035087719298</v>
       </c>
       <c r="L27" s="15">
-        <v>19.565217391304</v>
+        <v>27.450980392156</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>28</v>
@@ -1426,34 +1426,34 @@
         <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D28" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E28" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="F28" s="14">
         <v>47</v>
       </c>
       <c r="G28" s="14">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H28" s="15">
-        <v>-2.083333333333</v>
+        <v>17.5</v>
       </c>
       <c r="I28" s="14">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="J28" s="14">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K28" s="15">
-        <v>-7.526881720430</v>
+        <v>-5.940594059405</v>
       </c>
       <c r="L28" s="15">
-        <v>26.470588235294</v>
+        <v>20.253164556962</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>28</v>
@@ -1467,40 +1467,40 @@
         <v>35</v>
       </c>
       <c r="C29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="14">
         <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G29" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H29" s="15">
-        <v>-41.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="I29" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J29" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K29" s="15">
-        <v>-31.818181818181</v>
+        <v>-25</v>
       </c>
       <c r="L29" s="15">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-67.391304347826</v>
+        <v>-63.265306122449</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.140625</v>
+        <v>-94.019933554817</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,66 +1517,66 @@
         <v>50</v>
       </c>
       <c r="F30" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G30" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H30" s="15">
-        <v>-58.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="I30" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J30" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K30" s="15">
-        <v>-36.842105263157</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L30" s="15">
-        <v>-45.454545454545</v>
+        <v>-40</v>
       </c>
       <c r="M30" s="15">
-        <v>-68.421052631578</v>
+        <v>-63.414634146341</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.081967213114</v>
+        <v>-94.718309859154</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="14">
         <v>2</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F31" s="14">
-        <v>4</v>
-      </c>
       <c r="G31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I31" s="14">
         <v>10</v>
       </c>
       <c r="J31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>28</v>
@@ -1611,31 +1611,31 @@
         <v>38</v>
       </c>
       <c r="D33" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" s="15">
         <v>-100</v>
       </c>
       <c r="F33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" s="15">
-        <v>100</v>
+        <v>-75</v>
       </c>
       <c r="I33" s="14">
         <v>5</v>
       </c>
       <c r="J33" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>28</v>

--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,9 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -251,9 +254,6 @@
   </si>
   <si>
     <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -851,738 +851,738 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H14" s="15">
-        <v>-71.428571428571</v>
+        <v>-80</v>
       </c>
       <c r="I14" s="14">
         <v>4</v>
       </c>
       <c r="J14" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K14" s="15">
-        <v>-63.636363636363</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="L14" s="15">
-        <v>-69.230769230769</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M14" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N14" s="15">
-        <v>-94.736842105263</v>
+        <v>-95.061728395061</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F15" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G15" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H15" s="15">
-        <v>73.684210526315</v>
+        <v>105.555555555556</v>
       </c>
       <c r="I15" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J15" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>36.734693877551</v>
       </c>
       <c r="L15" s="15">
-        <v>130.769230769231</v>
+        <v>109.375</v>
       </c>
       <c r="M15" s="15">
-        <v>57.894736842105</v>
+        <v>71.794871794871</v>
       </c>
       <c r="N15" s="15">
-        <v>-38.144329896907</v>
+        <v>-37.962962962963</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E16" s="15">
-        <v>14.814814814814</v>
+        <v>10</v>
       </c>
       <c r="F16" s="14">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G16" s="14">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H16" s="15">
-        <v>17.886178861788</v>
+        <v>9.523809523809</v>
       </c>
       <c r="I16" s="14">
-        <v>308</v>
+        <v>340</v>
       </c>
       <c r="J16" s="14">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="K16" s="15">
-        <v>21.259842519685</v>
+        <v>19.718309859154</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.694376528117</v>
+        <v>-24.611973392461</v>
       </c>
       <c r="M16" s="15">
-        <v>-37.777777777777</v>
+        <v>-38.405797101449</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.085106382978</v>
+        <v>-88.427501701838</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D17" s="14">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E17" s="15">
-        <v>-17.582417582417</v>
+        <v>-14.130434782608</v>
       </c>
       <c r="F17" s="14">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="G17" s="14">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H17" s="15">
-        <v>-19.174041297935</v>
+        <v>-11.370262390670</v>
       </c>
       <c r="I17" s="14">
-        <v>623</v>
+        <v>711</v>
       </c>
       <c r="J17" s="14">
-        <v>641</v>
+        <v>733</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.808112324492</v>
+        <v>-3.001364256480</v>
       </c>
       <c r="L17" s="15">
-        <v>-1.579778830963</v>
+        <v>0.994318181818</v>
       </c>
       <c r="M17" s="15">
-        <v>39.686098654708</v>
+        <v>39.411764705882</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.381756756756</v>
+        <v>-46.541353383458</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
         <v>33</v>
       </c>
       <c r="D18" s="14">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E18" s="15">
-        <v>-10.810810810810</v>
+        <v>13.793103448275</v>
       </c>
       <c r="F18" s="14">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G18" s="14">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H18" s="15">
-        <v>4.580152671755</v>
+        <v>8.208955223880</v>
       </c>
       <c r="I18" s="14">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="J18" s="14">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="K18" s="15">
-        <v>2.473498233215</v>
+        <v>5.128205128205</v>
       </c>
       <c r="L18" s="15">
-        <v>-9.375</v>
+        <v>-8.379888268156</v>
       </c>
       <c r="M18" s="15">
-        <v>-31.116389548693</v>
+        <v>-30.655391120507</v>
       </c>
       <c r="N18" s="15">
-        <v>-83.409610983981</v>
+        <v>-83.534136546184</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D19" s="14">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="E19" s="15">
-        <v>-32.142857142857</v>
+        <v>-8.080808080808</v>
       </c>
       <c r="F19" s="14">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="G19" s="14">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.405835543766</v>
+        <v>-12.787723785166</v>
       </c>
       <c r="I19" s="14">
-        <v>730</v>
+        <v>827</v>
       </c>
       <c r="J19" s="14">
-        <v>747</v>
+        <v>846</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.275769745649</v>
+        <v>-2.245862884160</v>
       </c>
       <c r="L19" s="15">
-        <v>-14.419695193434</v>
+        <v>-13.943808532778</v>
       </c>
       <c r="M19" s="15">
-        <v>30.590339892665</v>
+        <v>31.269841269841</v>
       </c>
       <c r="N19" s="15">
-        <v>-20.995670995671</v>
+        <v>-20.173745173745</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D20" s="14">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E20" s="15">
-        <v>-45.454545454545</v>
+        <v>47.368421052631</v>
       </c>
       <c r="F20" s="14">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G20" s="14">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H20" s="15">
-        <v>-16.831683168316</v>
+        <v>-12.745098039215</v>
       </c>
       <c r="I20" s="14">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="J20" s="14">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="K20" s="15">
-        <v>-4.663212435233</v>
+        <v>-0.471698113207</v>
       </c>
       <c r="L20" s="15">
-        <v>-30.303030303030</v>
+        <v>-25.704225352112</v>
       </c>
       <c r="M20" s="15">
-        <v>-8.457711442786</v>
+        <v>-4.090909090909</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.014925373134</v>
+        <v>-88.835978835978</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="D21" s="17">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.846905537459</v>
+        <v>-2.166064981949</v>
       </c>
       <c r="F21" s="17">
-        <v>1009</v>
+        <v>1056</v>
       </c>
       <c r="G21" s="17">
-        <v>1097</v>
+        <v>1124</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.021877848678</v>
+        <v>-6.049822064056</v>
       </c>
       <c r="I21" s="17">
-        <v>2199</v>
+        <v>2488</v>
       </c>
       <c r="J21" s="17">
-        <v>2174</v>
+        <v>2451</v>
       </c>
       <c r="K21" s="18">
-        <v>1.149954001839</v>
+        <v>1.509587923296</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.668784749801</v>
+        <v>-11.269614835948</v>
       </c>
       <c r="M21" s="18">
-        <v>1.056985294117</v>
+        <v>1.883701883701</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.470865001809</v>
+        <v>-73.461333333333</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F22" s="14">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G22" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H22" s="15">
-        <v>29.166666666666</v>
+        <v>47.058823529411</v>
       </c>
       <c r="I22" s="14">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J22" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K22" s="15">
-        <v>5.769230769230</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L22" s="15">
-        <v>-15.384615384615</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="M22" s="15">
-        <v>-20.289855072463</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="14">
+        <v>25</v>
+      </c>
+      <c r="D23" s="14">
+        <v>35</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-28.571428571428</v>
+      </c>
+      <c r="F23" s="14">
+        <v>105</v>
+      </c>
+      <c r="G23" s="14">
+        <v>122</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-13.934426229508</v>
+      </c>
+      <c r="I23" s="14">
+        <v>227</v>
+      </c>
+      <c r="J23" s="14">
+        <v>265</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-14.339622641509</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-10.980392156862</v>
+      </c>
+      <c r="M23" s="15">
+        <v>36.746987951807</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C23" s="14">
-        <v>21</v>
-      </c>
-      <c r="D23" s="14">
-        <v>34</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-38.235294117647</v>
-      </c>
-      <c r="F23" s="14">
-        <v>90</v>
-      </c>
-      <c r="G23" s="14">
-        <v>119</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-24.369747899159</v>
-      </c>
-      <c r="I23" s="14">
-        <v>197</v>
-      </c>
-      <c r="J23" s="14">
-        <v>230</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-14.347826086956</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-15.450643776824</v>
-      </c>
-      <c r="M23" s="15">
-        <v>35.862068965517</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="D24" s="14">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.063063063063</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>827</v>
+        <v>852</v>
       </c>
       <c r="G24" s="14">
-        <v>805</v>
+        <v>839</v>
       </c>
       <c r="H24" s="15">
-        <v>2.732919254658</v>
+        <v>1.549463647199</v>
       </c>
       <c r="I24" s="14">
-        <v>1778</v>
+        <v>2009</v>
       </c>
       <c r="J24" s="14">
-        <v>1747</v>
+        <v>1970</v>
       </c>
       <c r="K24" s="15">
-        <v>1.774470520892</v>
+        <v>1.979695431472</v>
       </c>
       <c r="L24" s="15">
-        <v>-10.337871911245</v>
+        <v>-8.432087511394</v>
       </c>
       <c r="M24" s="15">
-        <v>24.335664335664</v>
+        <v>23.402948402948</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D25" s="14">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E25" s="15">
-        <v>-26.315789473684</v>
+        <v>-10.588235294117</v>
       </c>
       <c r="F25" s="14">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G25" s="14">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="H25" s="15">
-        <v>-9.467455621301</v>
+        <v>-14.325842696629</v>
       </c>
       <c r="I25" s="14">
-        <v>644</v>
+        <v>723</v>
       </c>
       <c r="J25" s="14">
-        <v>694</v>
+        <v>779</v>
       </c>
       <c r="K25" s="15">
-        <v>-7.204610951008</v>
+        <v>-7.188703465982</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.203252032520</v>
+        <v>-25.232678386763</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D26" s="14">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.454545454545</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F26" s="14">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="G26" s="14">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="H26" s="15">
-        <v>8.624708624708</v>
+        <v>-1.118568232662</v>
       </c>
       <c r="I26" s="14">
-        <v>912</v>
+        <v>1021</v>
       </c>
       <c r="J26" s="14">
-        <v>861</v>
+        <v>982</v>
       </c>
       <c r="K26" s="15">
-        <v>5.923344947735</v>
+        <v>3.971486761710</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.201680672268</v>
+        <v>-5.462962962962</v>
       </c>
       <c r="M26" s="15">
-        <v>-17.316409791477</v>
+        <v>-19.352290679304</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E27" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F27" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G27" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" s="15">
-        <v>56.521739130434</v>
+        <v>70.833333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J27" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K27" s="15">
-        <v>14.035087719298</v>
+        <v>15.873015873015</v>
       </c>
       <c r="L27" s="15">
-        <v>27.450980392156</v>
+        <v>19.672131147541</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D28" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>25</v>
+        <v>240</v>
       </c>
       <c r="F28" s="14">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G28" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H28" s="15">
-        <v>17.5</v>
+        <v>44.736842105263</v>
       </c>
       <c r="I28" s="14">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="J28" s="14">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="K28" s="15">
-        <v>-5.940594059405</v>
+        <v>4.716981132075</v>
       </c>
       <c r="L28" s="15">
-        <v>20.253164556962</v>
+        <v>26.136363636363</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="14">
+        <v>36</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
         <v>3</v>
       </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
       <c r="E29" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>8</v>
       </c>
       <c r="G29" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H29" s="15">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I29" s="14">
         <v>18</v>
       </c>
       <c r="J29" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K29" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-33.333333333333</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M29" s="15">
-        <v>-63.265306122449</v>
+        <v>-69.491525423728</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.019933554817</v>
+        <v>-94.461538461538</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="14">
+        <v>37</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>3</v>
       </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
       <c r="E30" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>7</v>
       </c>
       <c r="G30" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H30" s="15">
-        <v>-30</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I30" s="14">
         <v>15</v>
       </c>
       <c r="J30" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K30" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="L30" s="15">
-        <v>-40</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="M30" s="15">
-        <v>-63.414634146341</v>
+        <v>-68.75</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.718309859154</v>
+        <v>-95.098039215686</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="13" t="s">
         <v>38</v>
       </c>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
       <c r="D31" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H31" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="I31" s="14">
+        <v>11</v>
+      </c>
+      <c r="J31" s="14">
         <v>10</v>
       </c>
-      <c r="J31" s="14">
-        <v>6</v>
-      </c>
       <c r="K31" s="15">
-        <v>66.666666666666</v>
+        <v>10</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,41 +1607,41 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="14">
-        <v>3</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="C33" s="14">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="14">
         <v>4</v>
       </c>
       <c r="H33" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I33" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" s="14">
         <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L33" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>708</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>20509</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>9978</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>14993</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>8788</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>12552</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>68033</v>

--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -199,67 +199,67 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
+    <t>Traffic Statistics</t>
+  </si>
+  <si>
+    <t>Traffic Fatalities</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>Traffic Statistics</t>
-  </si>
-  <si>
-    <t>Traffic Fatalities</t>
   </si>
   <si>
     <t>Historical Perspective</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,743 +851,743 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H14" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K14" s="15">
-        <v>-73.333333333333</v>
+        <v>-68.75</v>
       </c>
       <c r="L14" s="15">
-        <v>-71.428571428571</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="M14" s="15">
-        <v>-77.777777777777</v>
+        <v>-78.260869565217</v>
       </c>
       <c r="N14" s="15">
-        <v>-95.061728395061</v>
+        <v>-94.186046511627</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F15" s="14">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G15" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H15" s="15">
-        <v>105.555555555556</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J15" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K15" s="15">
-        <v>36.734693877551</v>
+        <v>40.384615384615</v>
       </c>
       <c r="L15" s="15">
-        <v>109.375</v>
+        <v>87.179487179487</v>
       </c>
       <c r="M15" s="15">
-        <v>71.794871794871</v>
+        <v>73.809523809523</v>
       </c>
       <c r="N15" s="15">
-        <v>-37.962962962963</v>
+        <v>-39.669421487603</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D16" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E16" s="15">
-        <v>10</v>
+        <v>11.428571428571</v>
       </c>
       <c r="F16" s="14">
         <v>138</v>
       </c>
       <c r="G16" s="14">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H16" s="15">
-        <v>9.523809523809</v>
+        <v>15</v>
       </c>
       <c r="I16" s="14">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="J16" s="14">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="K16" s="15">
-        <v>19.718309859154</v>
+        <v>18.495297805642</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.611973392461</v>
+        <v>-23.481781376518</v>
       </c>
       <c r="M16" s="15">
-        <v>-38.405797101449</v>
+        <v>-37.623762376237</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.427501701838</v>
+        <v>-88.322520852641</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D17" s="14">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="E17" s="15">
-        <v>-14.130434782608</v>
+        <v>17.1875</v>
       </c>
       <c r="F17" s="14">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="G17" s="14">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="H17" s="15">
-        <v>-11.370262390670</v>
+        <v>-5.740181268882</v>
       </c>
       <c r="I17" s="14">
-        <v>711</v>
+        <v>798</v>
       </c>
       <c r="J17" s="14">
-        <v>733</v>
+        <v>797</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.001364256480</v>
+        <v>0.125470514429</v>
       </c>
       <c r="L17" s="15">
-        <v>0.994318181818</v>
+        <v>1.269035532994</v>
       </c>
       <c r="M17" s="15">
-        <v>39.411764705882</v>
+        <v>41.238938053097</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.541353383458</v>
+        <v>-44.660194174757</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
+        <v>32</v>
+      </c>
+      <c r="D18" s="14">
         <v>33</v>
       </c>
-      <c r="D18" s="14">
-        <v>29</v>
-      </c>
       <c r="E18" s="15">
-        <v>13.793103448275</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="F18" s="14">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G18" s="14">
         <v>134</v>
       </c>
       <c r="H18" s="15">
-        <v>8.208955223880</v>
+        <v>5.223880597014</v>
       </c>
       <c r="I18" s="14">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="J18" s="14">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="K18" s="15">
-        <v>5.128205128205</v>
+        <v>4.057971014492</v>
       </c>
       <c r="L18" s="15">
-        <v>-8.379888268156</v>
+        <v>-7.235142118863</v>
       </c>
       <c r="M18" s="15">
-        <v>-30.655391120507</v>
+        <v>-32.136105860113</v>
       </c>
       <c r="N18" s="15">
-        <v>-83.534136546184</v>
+        <v>-83.562271062271</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D19" s="14">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E19" s="15">
-        <v>-8.080808080808</v>
+        <v>-10.091743119266</v>
       </c>
       <c r="F19" s="14">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="G19" s="14">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.787723785166</v>
+        <v>-15.180722891566</v>
       </c>
       <c r="I19" s="14">
-        <v>827</v>
+        <v>926</v>
       </c>
       <c r="J19" s="14">
-        <v>846</v>
+        <v>955</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.245862884160</v>
+        <v>-3.036649214659</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.943808532778</v>
+        <v>-11.641221374045</v>
       </c>
       <c r="M19" s="15">
-        <v>31.269841269841</v>
+        <v>30.056179775280</v>
       </c>
       <c r="N19" s="15">
-        <v>-20.173745173745</v>
+        <v>-18.985126859142</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D20" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E20" s="15">
-        <v>47.368421052631</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F20" s="14">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G20" s="14">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H20" s="15">
-        <v>-12.745098039215</v>
+        <v>-7.070707070707</v>
       </c>
       <c r="I20" s="14">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="J20" s="14">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="K20" s="15">
-        <v>-0.471698113207</v>
+        <v>1.282051282051</v>
       </c>
       <c r="L20" s="15">
-        <v>-25.704225352112</v>
+        <v>-24.522292993630</v>
       </c>
       <c r="M20" s="15">
-        <v>-4.090909090909</v>
+        <v>-1.659751037344</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.835978835978</v>
+        <v>-88.444661140906</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D21" s="17">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.166064981949</v>
+        <v>2.621722846441</v>
       </c>
       <c r="F21" s="17">
-        <v>1056</v>
+        <v>1068</v>
       </c>
       <c r="G21" s="17">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.049822064056</v>
+        <v>-4.897595725734</v>
       </c>
       <c r="I21" s="17">
-        <v>2488</v>
+        <v>2776</v>
       </c>
       <c r="J21" s="17">
-        <v>2451</v>
+        <v>2718</v>
       </c>
       <c r="K21" s="18">
-        <v>1.509587923296</v>
+        <v>2.133922001471</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.269614835948</v>
+        <v>-10.074505992873</v>
       </c>
       <c r="M21" s="18">
-        <v>1.883701883701</v>
+        <v>2.133922001471</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.461333333333</v>
+        <v>-72.954014029618</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="14">
+        <v>5</v>
+      </c>
+      <c r="D22" s="14">
+        <v>6</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="F22" s="14">
+        <v>24</v>
+      </c>
+      <c r="G22" s="14">
+        <v>14</v>
+      </c>
+      <c r="H22" s="15">
+        <v>71.428571428571</v>
+      </c>
+      <c r="I22" s="14">
+        <v>62</v>
+      </c>
+      <c r="J22" s="14">
+        <v>60</v>
+      </c>
+      <c r="K22" s="15">
+        <v>3.333333333333</v>
+      </c>
+      <c r="L22" s="15">
+        <v>-12.676056338028</v>
+      </c>
+      <c r="M22" s="15">
+        <v>-22.5</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="C22" s="14">
-        <v>3</v>
-      </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>50</v>
-      </c>
-      <c r="F22" s="14">
-        <v>25</v>
-      </c>
-      <c r="G22" s="14">
-        <v>17</v>
-      </c>
-      <c r="H22" s="15">
-        <v>47.058823529411</v>
-      </c>
-      <c r="I22" s="14">
-        <v>57</v>
-      </c>
-      <c r="J22" s="14">
-        <v>54</v>
-      </c>
-      <c r="K22" s="15">
-        <v>5.555555555555</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-17.391304347826</v>
-      </c>
-      <c r="M22" s="15">
-        <v>-25</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D23" s="14">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E23" s="15">
-        <v>-28.571428571428</v>
+        <v>63.157894736842</v>
       </c>
       <c r="F23" s="14">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G23" s="14">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H23" s="15">
-        <v>-13.934426229508</v>
+        <v>-7.826086956521</v>
       </c>
       <c r="I23" s="14">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="J23" s="14">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="K23" s="15">
-        <v>-14.339622641509</v>
+        <v>-7.394366197183</v>
       </c>
       <c r="L23" s="15">
-        <v>-10.980392156862</v>
+        <v>-8.041958041958</v>
       </c>
       <c r="M23" s="15">
-        <v>36.746987951807</v>
+        <v>42.934782608695</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D24" s="14">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>5.607476635514</v>
       </c>
       <c r="F24" s="14">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G24" s="14">
-        <v>839</v>
+        <v>850</v>
       </c>
       <c r="H24" s="15">
-        <v>1.549463647199</v>
+        <v>2.117647058823</v>
       </c>
       <c r="I24" s="14">
-        <v>2009</v>
+        <v>2228</v>
       </c>
       <c r="J24" s="14">
-        <v>1970</v>
+        <v>2184</v>
       </c>
       <c r="K24" s="15">
-        <v>1.979695431472</v>
+        <v>2.014652014652</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.432087511394</v>
+        <v>-8.388157894736</v>
       </c>
       <c r="M24" s="15">
-        <v>23.402948402948</v>
+        <v>22.687224669603</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D25" s="14">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E25" s="15">
-        <v>-10.588235294117</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="14">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="G25" s="14">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H25" s="15">
-        <v>-14.325842696629</v>
+        <v>-19.777158774373</v>
       </c>
       <c r="I25" s="14">
-        <v>723</v>
+        <v>787</v>
       </c>
       <c r="J25" s="14">
-        <v>779</v>
+        <v>854</v>
       </c>
       <c r="K25" s="15">
-        <v>-7.188703465982</v>
+        <v>-7.845433255269</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.232678386763</v>
+        <v>-27.598896044158</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="D26" s="14">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E26" s="15">
-        <v>-9.090909090909</v>
+        <v>6.451612903225</v>
       </c>
       <c r="F26" s="14">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="G26" s="14">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="H26" s="15">
-        <v>-1.118568232662</v>
+        <v>-1.098901098901</v>
       </c>
       <c r="I26" s="14">
-        <v>1021</v>
+        <v>1146</v>
       </c>
       <c r="J26" s="14">
-        <v>982</v>
+        <v>1106</v>
       </c>
       <c r="K26" s="15">
-        <v>3.971486761710</v>
+        <v>3.616636528028</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.462962962962</v>
+        <v>-5.834018077239</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.352290679304</v>
+        <v>-19.124911785462</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>33.333333333333</v>
+        <v>75</v>
       </c>
       <c r="F27" s="14">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G27" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H27" s="15">
-        <v>70.833333333333</v>
+        <v>71.428571428571</v>
       </c>
       <c r="I27" s="14">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="J27" s="14">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K27" s="15">
-        <v>15.873015873015</v>
+        <v>20.895522388059</v>
       </c>
       <c r="L27" s="15">
-        <v>19.672131147541</v>
+        <v>17.391304347826</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E28" s="15">
-        <v>240</v>
+        <v>-12.5</v>
       </c>
       <c r="F28" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G28" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H28" s="15">
-        <v>44.736842105263</v>
+        <v>46.341463414634</v>
       </c>
       <c r="I28" s="14">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J28" s="14">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="K28" s="15">
-        <v>4.716981132075</v>
+        <v>0.819672131147</v>
       </c>
       <c r="L28" s="15">
-        <v>26.136363636363</v>
+        <v>25.510204081632</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+        <v>35</v>
+      </c>
+      <c r="C29" s="14">
+        <v>6</v>
       </c>
       <c r="D29" s="14">
         <v>3</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F29" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G29" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H29" s="15">
-        <v>-27.272727272727</v>
+        <v>30</v>
       </c>
       <c r="I29" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J29" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K29" s="15">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="L29" s="15">
-        <v>-35.714285714285</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="M29" s="15">
-        <v>-69.491525423728</v>
+        <v>-64.179104477611</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.461538461538</v>
+        <v>-93.258426966292</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="C30" s="14">
+        <v>6</v>
       </c>
       <c r="D30" s="14">
         <v>3</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F30" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G30" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H30" s="15">
+        <v>20</v>
+      </c>
+      <c r="I30" s="14">
+        <v>21</v>
+      </c>
+      <c r="J30" s="14">
+        <v>27</v>
+      </c>
+      <c r="K30" s="15">
+        <v>-22.222222222222</v>
+      </c>
+      <c r="L30" s="15">
         <v>-36.363636363636</v>
       </c>
-      <c r="I30" s="14">
-        <v>15</v>
-      </c>
-      <c r="J30" s="14">
-        <v>24</v>
-      </c>
-      <c r="K30" s="15">
-        <v>-37.5</v>
-      </c>
-      <c r="L30" s="15">
-        <v>-42.307692307692</v>
-      </c>
       <c r="M30" s="15">
-        <v>-68.75</v>
+        <v>-61.818181818181</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.098039215686</v>
+        <v>-93.693693693693</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" s="14">
+        <v>3</v>
+      </c>
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="14">
-        <v>4</v>
-      </c>
       <c r="E31" s="15">
-        <v>-75</v>
+        <v>200</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G31" s="14">
         <v>6</v>
       </c>
       <c r="H31" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I31" s="14">
+        <v>15</v>
+      </c>
+      <c r="J31" s="14">
         <v>11</v>
       </c>
-      <c r="J31" s="14">
-        <v>10</v>
-      </c>
       <c r="K31" s="15">
-        <v>10</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L31" s="15">
-        <v>10</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1605,25 +1605,25 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
+      <c r="D33" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="14">
         <v>1</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33" s="14">
-        <v>2</v>
       </c>
       <c r="G33" s="14">
         <v>4</v>
       </c>
       <c r="H33" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I33" s="14">
         <v>6</v>
@@ -1638,10 +1638,10 @@
         <v>50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>708</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>20509</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>9978</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>14993</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>8788</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>12552</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>68033</v>

--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,9 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -257,9 +260,6 @@
   </si>
   <si>
     <t>Traffic Fatalities</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Historical Perspective</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,720 +851,720 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="14">
         <v>1</v>
       </c>
       <c r="E14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I14" s="14">
         <v>5</v>
       </c>
       <c r="J14" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K14" s="15">
-        <v>-68.75</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="L14" s="15">
         <v>-70.588235294117</v>
       </c>
       <c r="M14" s="15">
-        <v>-78.260869565217</v>
+        <v>-80</v>
       </c>
       <c r="N14" s="15">
-        <v>-94.186046511627</v>
+        <v>-94.791666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>66.666666666666</v>
+        <v>125</v>
       </c>
       <c r="F15" s="14">
         <v>30</v>
       </c>
       <c r="G15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="I15" s="14">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J15" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K15" s="15">
-        <v>40.384615384615</v>
+        <v>46.428571428571</v>
       </c>
       <c r="L15" s="15">
-        <v>87.179487179487</v>
+        <v>86.363636363636</v>
       </c>
       <c r="M15" s="15">
-        <v>73.809523809523</v>
+        <v>67.346938775510</v>
       </c>
       <c r="N15" s="15">
-        <v>-39.669421487603</v>
+        <v>-37.878787878787</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D16" s="14">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E16" s="15">
-        <v>11.428571428571</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="F16" s="14">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G16" s="14">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="H16" s="15">
-        <v>15</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="I16" s="14">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="J16" s="14">
-        <v>319</v>
+        <v>362</v>
       </c>
       <c r="K16" s="15">
-        <v>18.495297805642</v>
+        <v>12.430939226519</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.481781376518</v>
+        <v>-24.349442379182</v>
       </c>
       <c r="M16" s="15">
-        <v>-37.623762376237</v>
+        <v>-39.162929745889</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.322520852641</v>
+        <v>-88.515801354401</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D17" s="14">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E17" s="15">
-        <v>17.1875</v>
+        <v>9.722222222222</v>
       </c>
       <c r="F17" s="14">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="G17" s="14">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="H17" s="15">
-        <v>-5.740181268882</v>
+        <v>1.567398119122</v>
       </c>
       <c r="I17" s="14">
-        <v>798</v>
+        <v>884</v>
       </c>
       <c r="J17" s="14">
-        <v>797</v>
+        <v>869</v>
       </c>
       <c r="K17" s="15">
-        <v>0.125470514429</v>
+        <v>1.726121979286</v>
       </c>
       <c r="L17" s="15">
-        <v>1.269035532994</v>
+        <v>2.078521939953</v>
       </c>
       <c r="M17" s="15">
-        <v>41.238938053097</v>
+        <v>41.214057507987</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.660194174757</v>
+        <v>-44.402515723270</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D18" s="14">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E18" s="15">
-        <v>-3.030303030303</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F18" s="14">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="G18" s="14">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="H18" s="15">
-        <v>5.223880597014</v>
+        <v>-0.826446280991</v>
       </c>
       <c r="I18" s="14">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="J18" s="14">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="K18" s="15">
-        <v>4.057971014492</v>
+        <v>4.087193460490</v>
       </c>
       <c r="L18" s="15">
-        <v>-7.235142118863</v>
+        <v>-7.506053268765</v>
       </c>
       <c r="M18" s="15">
-        <v>-32.136105860113</v>
+        <v>-34.589041095890</v>
       </c>
       <c r="N18" s="15">
-        <v>-83.562271062271</v>
+        <v>-83.989941324392</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D19" s="14">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E19" s="15">
-        <v>-10.091743119266</v>
+        <v>-17.543859649122</v>
       </c>
       <c r="F19" s="14">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="G19" s="14">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="H19" s="15">
-        <v>-15.180722891566</v>
+        <v>-15.437788018433</v>
       </c>
       <c r="I19" s="14">
-        <v>926</v>
+        <v>1028</v>
       </c>
       <c r="J19" s="14">
-        <v>955</v>
+        <v>1069</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.036649214659</v>
+        <v>-3.835360149672</v>
       </c>
       <c r="L19" s="15">
-        <v>-11.641221374045</v>
+        <v>-12.211784799316</v>
       </c>
       <c r="M19" s="15">
-        <v>30.056179775280</v>
+        <v>30.955414012738</v>
       </c>
       <c r="N19" s="15">
-        <v>-18.985126859142</v>
+        <v>-18.412698412698</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D20" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E20" s="15">
-        <v>9.090909090909</v>
+        <v>47.368421052631</v>
       </c>
       <c r="F20" s="14">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G20" s="14">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H20" s="15">
-        <v>-7.070707070707</v>
+        <v>6.451612903225</v>
       </c>
       <c r="I20" s="14">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="J20" s="14">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="K20" s="15">
-        <v>1.282051282051</v>
+        <v>4.743083003952</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.522292993630</v>
+        <v>-20.420420420420</v>
       </c>
       <c r="M20" s="15">
-        <v>-1.659751037344</v>
+        <v>-2.214022140221</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.444661140906</v>
+        <v>-88.201246660730</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="D21" s="17">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="E21" s="18">
-        <v>2.621722846441</v>
+        <v>-4</v>
       </c>
       <c r="F21" s="17">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="G21" s="17">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.897595725734</v>
+        <v>-4.795737122557</v>
       </c>
       <c r="I21" s="17">
-        <v>2776</v>
+        <v>3053</v>
       </c>
       <c r="J21" s="17">
-        <v>2718</v>
+        <v>2993</v>
       </c>
       <c r="K21" s="18">
-        <v>2.133922001471</v>
+        <v>2.004677581022</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.074505992873</v>
+        <v>-9.727971614429</v>
       </c>
       <c r="M21" s="18">
-        <v>2.133922001471</v>
+        <v>1.462279827185</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.954014029618</v>
+        <v>-72.871867780344</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
         <v>5</v>
       </c>
       <c r="D22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F22" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H22" s="15">
-        <v>71.428571428571</v>
+        <v>5.263157894736</v>
       </c>
       <c r="I22" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J22" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K22" s="15">
-        <v>3.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>-12.676056338028</v>
+        <v>-10.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>-22.5</v>
+        <v>-24.719101123595</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="14">
+        <v>15</v>
+      </c>
+      <c r="D23" s="14">
+        <v>17</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-11.764705882352</v>
+      </c>
+      <c r="F23" s="14">
+        <v>99</v>
+      </c>
+      <c r="G23" s="14">
+        <v>105</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-5.714285714285</v>
+      </c>
+      <c r="I23" s="14">
+        <v>281</v>
+      </c>
+      <c r="J23" s="14">
+        <v>301</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-6.644518272425</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-11.635220125786</v>
+      </c>
+      <c r="M23" s="15">
+        <v>40.5</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C23" s="14">
-        <v>31</v>
-      </c>
-      <c r="D23" s="14">
-        <v>19</v>
-      </c>
-      <c r="E23" s="15">
-        <v>63.157894736842</v>
-      </c>
-      <c r="F23" s="14">
-        <v>106</v>
-      </c>
-      <c r="G23" s="14">
-        <v>115</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-7.826086956521</v>
-      </c>
-      <c r="I23" s="14">
-        <v>263</v>
-      </c>
-      <c r="J23" s="14">
-        <v>284</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-7.394366197183</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-8.041958041958</v>
-      </c>
-      <c r="M23" s="15">
-        <v>42.934782608695</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D24" s="14">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="E24" s="15">
-        <v>5.607476635514</v>
+        <v>7.725321888412</v>
       </c>
       <c r="F24" s="14">
-        <v>868</v>
+        <v>896</v>
       </c>
       <c r="G24" s="14">
-        <v>850</v>
+        <v>892</v>
       </c>
       <c r="H24" s="15">
-        <v>2.117647058823</v>
+        <v>0.448430493273</v>
       </c>
       <c r="I24" s="14">
-        <v>2228</v>
+        <v>2476</v>
       </c>
       <c r="J24" s="14">
-        <v>2184</v>
+        <v>2417</v>
       </c>
       <c r="K24" s="15">
-        <v>2.014652014652</v>
+        <v>2.441042614811</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.388157894736</v>
+        <v>-8.769344141488</v>
       </c>
       <c r="M24" s="15">
-        <v>22.687224669603</v>
+        <v>23.306772908366</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="D25" s="14">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="E25" s="15">
-        <v>-20</v>
+        <v>-17.117117117117</v>
       </c>
       <c r="F25" s="14">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="G25" s="14">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="H25" s="15">
-        <v>-19.777158774373</v>
+        <v>-17.759562841530</v>
       </c>
       <c r="I25" s="14">
-        <v>787</v>
+        <v>877</v>
       </c>
       <c r="J25" s="14">
-        <v>854</v>
+        <v>965</v>
       </c>
       <c r="K25" s="15">
-        <v>-7.845433255269</v>
+        <v>-9.119170984455</v>
       </c>
       <c r="L25" s="15">
-        <v>-27.598896044158</v>
+        <v>-28.055783429040</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D26" s="14">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="E26" s="15">
-        <v>6.451612903225</v>
+        <v>11.926605504587</v>
       </c>
       <c r="F26" s="14">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G26" s="14">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="H26" s="15">
-        <v>-1.098901098901</v>
+        <v>-2.155172413793</v>
       </c>
       <c r="I26" s="14">
-        <v>1146</v>
+        <v>1271</v>
       </c>
       <c r="J26" s="14">
-        <v>1106</v>
+        <v>1215</v>
       </c>
       <c r="K26" s="15">
-        <v>3.616636528028</v>
+        <v>4.609053497942</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.834018077239</v>
+        <v>-3.346007604562</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.124911785462</v>
+        <v>-18.785942492012</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>9</v>
+      </c>
+      <c r="D27" s="14">
         <v>7</v>
       </c>
-      <c r="D27" s="14">
-        <v>4</v>
-      </c>
       <c r="E27" s="15">
-        <v>75</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F27" s="14">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G27" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H27" s="15">
-        <v>71.428571428571</v>
+        <v>40</v>
       </c>
       <c r="I27" s="14">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J27" s="14">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K27" s="15">
-        <v>20.895522388059</v>
+        <v>22.972972972973</v>
       </c>
       <c r="L27" s="15">
-        <v>17.391304347826</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" s="14">
         <v>16</v>
       </c>
       <c r="E28" s="15">
-        <v>-12.5</v>
+        <v>-6.25</v>
       </c>
       <c r="F28" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G28" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H28" s="15">
-        <v>46.341463414634</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I28" s="14">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="J28" s="14">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="K28" s="15">
-        <v>0.819672131147</v>
+        <v>-5.072463768115</v>
       </c>
       <c r="L28" s="15">
-        <v>25.510204081632</v>
+        <v>19.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="14">
+        <v>5</v>
+      </c>
+      <c r="D29" s="14">
+        <v>5</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>14</v>
+      </c>
+      <c r="G29" s="14">
+        <v>13</v>
+      </c>
+      <c r="H29" s="15">
+        <v>7.692307692307</v>
+      </c>
+      <c r="I29" s="14">
+        <v>29</v>
+      </c>
+      <c r="J29" s="14">
         <v>35</v>
       </c>
-      <c r="C29" s="14">
-        <v>6</v>
-      </c>
-      <c r="D29" s="14">
-        <v>3</v>
-      </c>
-      <c r="E29" s="15">
-        <v>100</v>
-      </c>
-      <c r="F29" s="14">
-        <v>13</v>
-      </c>
-      <c r="G29" s="14">
-        <v>10</v>
-      </c>
-      <c r="H29" s="15">
-        <v>30</v>
-      </c>
-      <c r="I29" s="14">
-        <v>24</v>
-      </c>
-      <c r="J29" s="14">
-        <v>30</v>
-      </c>
       <c r="K29" s="15">
-        <v>-20</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="L29" s="15">
-        <v>-35.135135135135</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="M29" s="15">
-        <v>-64.179104477611</v>
+        <v>-61.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.258426966292</v>
+        <v>-92.713567839196</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14">
+        <v>13</v>
+      </c>
+      <c r="G30" s="14">
         <v>12</v>
       </c>
-      <c r="G30" s="14">
-        <v>10</v>
-      </c>
       <c r="H30" s="15">
-        <v>20</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I30" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J30" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K30" s="15">
-        <v>-22.222222222222</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="L30" s="15">
-        <v>-36.363636363636</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="M30" s="15">
-        <v>-61.818181818181</v>
+        <v>-59.016393442622</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.693693693693</v>
+        <v>-93.297587131367</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="14">
-        <v>3</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>200</v>
+        <v>38</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F31" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G31" s="14">
         <v>6</v>
       </c>
       <c r="H31" s="15">
-        <v>33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I31" s="14">
         <v>15</v>
@@ -1579,15 +1579,15 @@
         <v>36.363636363636</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1605,16 +1605,16 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>28</v>
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1629,19 +1629,19 @@
         <v>6</v>
       </c>
       <c r="J33" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>708</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>20509</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>9978</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>14993</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>8788</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>12552</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>68033</v>

--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -861,31 +861,31 @@
         <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H14" s="15">
-        <v>-75</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I14" s="14">
         <v>5</v>
       </c>
       <c r="J14" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K14" s="15">
-        <v>-70.588235294117</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="L14" s="15">
-        <v>-70.588235294117</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="M14" s="15">
-        <v>-80</v>
+        <v>-80.769230769230</v>
       </c>
       <c r="N14" s="15">
-        <v>-94.791666666666</v>
+        <v>-95.412844036697</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D15" s="14">
         <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="F15" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G15" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H15" s="15">
-        <v>87.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J15" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K15" s="15">
-        <v>46.428571428571</v>
+        <v>45</v>
       </c>
       <c r="L15" s="15">
-        <v>86.363636363636</v>
+        <v>77.551020408163</v>
       </c>
       <c r="M15" s="15">
-        <v>67.346938775510</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>-37.878787878787</v>
+        <v>-37.857142857142</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D16" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E16" s="15">
-        <v>-30.232558139534</v>
+        <v>-14.634146341463</v>
       </c>
       <c r="F16" s="14">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G16" s="14">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="H16" s="15">
-        <v>-3.703703703703</v>
+        <v>-6.040268456375</v>
       </c>
       <c r="I16" s="14">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="J16" s="14">
-        <v>362</v>
+        <v>403</v>
       </c>
       <c r="K16" s="15">
-        <v>12.430939226519</v>
+        <v>10.669975186104</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.349442379182</v>
+        <v>-22.837370242214</v>
       </c>
       <c r="M16" s="15">
-        <v>-39.162929745889</v>
+        <v>-39.319727891156</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.515801354401</v>
+        <v>-88.382391247720</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D17" s="14">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E17" s="15">
-        <v>9.722222222222</v>
+        <v>2.222222222222</v>
       </c>
       <c r="F17" s="14">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="G17" s="14">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H17" s="15">
-        <v>1.567398119122</v>
+        <v>6.918238993710</v>
       </c>
       <c r="I17" s="14">
-        <v>884</v>
+        <v>982</v>
       </c>
       <c r="J17" s="14">
-        <v>869</v>
+        <v>959</v>
       </c>
       <c r="K17" s="15">
-        <v>1.726121979286</v>
+        <v>2.398331595411</v>
       </c>
       <c r="L17" s="15">
-        <v>2.078521939953</v>
+        <v>4.246284501061</v>
       </c>
       <c r="M17" s="15">
-        <v>41.214057507987</v>
+        <v>43.357664233576</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.402515723270</v>
+        <v>-44.769403824521</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D18" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E18" s="15">
-        <v>9.090909090909</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="14">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="G18" s="14">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="H18" s="15">
-        <v>-0.826446280991</v>
+        <v>0.892857142857</v>
       </c>
       <c r="I18" s="14">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="J18" s="14">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="K18" s="15">
-        <v>4.087193460490</v>
+        <v>4.050632911392</v>
       </c>
       <c r="L18" s="15">
-        <v>-7.506053268765</v>
+        <v>-7.013574660633</v>
       </c>
       <c r="M18" s="15">
-        <v>-34.589041095890</v>
+        <v>-34.86529318542</v>
       </c>
       <c r="N18" s="15">
-        <v>-83.989941324392</v>
+        <v>-84.300993124522</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D19" s="14">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="E19" s="15">
-        <v>-17.543859649122</v>
+        <v>5.813953488372</v>
       </c>
       <c r="F19" s="14">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="G19" s="14">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="H19" s="15">
-        <v>-15.437788018433</v>
+        <v>-5.392156862745</v>
       </c>
       <c r="I19" s="14">
-        <v>1028</v>
+        <v>1127</v>
       </c>
       <c r="J19" s="14">
-        <v>1069</v>
+        <v>1155</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.835360149672</v>
+        <v>-2.424242424242</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.211784799316</v>
+        <v>-10.413354531001</v>
       </c>
       <c r="M19" s="15">
-        <v>30.955414012738</v>
+        <v>28.068181818181</v>
       </c>
       <c r="N19" s="15">
-        <v>-18.412698412698</v>
+        <v>-19.095477386934</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D20" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E20" s="15">
-        <v>47.368421052631</v>
+        <v>20</v>
       </c>
       <c r="F20" s="14">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="G20" s="14">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H20" s="15">
-        <v>6.451612903225</v>
+        <v>32.941176470588</v>
       </c>
       <c r="I20" s="14">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="J20" s="14">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="K20" s="15">
-        <v>4.743083003952</v>
+        <v>6.474820143884</v>
       </c>
       <c r="L20" s="15">
-        <v>-20.420420420420</v>
+        <v>-18.904109589041</v>
       </c>
       <c r="M20" s="15">
-        <v>-2.214022140221</v>
+        <v>0.338983050847</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.201246660730</v>
+        <v>-87.813915191436</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="D21" s="17">
         <v>275</v>
       </c>
       <c r="E21" s="18">
-        <v>-4</v>
+        <v>-0.363636363636</v>
       </c>
       <c r="F21" s="17">
-        <v>1072</v>
+        <v>1118</v>
       </c>
       <c r="G21" s="17">
-        <v>1126</v>
+        <v>1094</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.795737122557</v>
+        <v>2.193784277879</v>
       </c>
       <c r="I21" s="17">
-        <v>3053</v>
+        <v>3354</v>
       </c>
       <c r="J21" s="17">
-        <v>2993</v>
+        <v>3268</v>
       </c>
       <c r="K21" s="18">
-        <v>2.004677581022</v>
+        <v>2.631578947368</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.727971614429</v>
+        <v>-8.159912376779</v>
       </c>
       <c r="M21" s="18">
-        <v>1.462279827185</v>
+        <v>1.329305135951</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.871867780344</v>
+        <v>-72.745002437835</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D22" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22" s="15">
-        <v>-28.571428571428</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F22" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G22" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H22" s="15">
-        <v>5.263157894736</v>
+        <v>-25</v>
       </c>
       <c r="I22" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J22" s="14">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-6.578947368421</v>
       </c>
       <c r="L22" s="15">
-        <v>-10.666666666666</v>
+        <v>-12.345679012345</v>
       </c>
       <c r="M22" s="15">
-        <v>-24.719101123595</v>
+        <v>-29.702970297029</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>29</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D23" s="14">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E23" s="15">
-        <v>-11.764705882352</v>
+        <v>10.714285714285</v>
       </c>
       <c r="F23" s="14">
+        <v>109</v>
+      </c>
+      <c r="G23" s="14">
         <v>99</v>
       </c>
-      <c r="G23" s="14">
-        <v>105</v>
-      </c>
       <c r="H23" s="15">
-        <v>-5.714285714285</v>
+        <v>10.101010101010</v>
       </c>
       <c r="I23" s="14">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="J23" s="14">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="K23" s="15">
-        <v>-6.644518272425</v>
+        <v>-3.647416413373</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.635220125786</v>
+        <v>-9.686609686609</v>
       </c>
       <c r="M23" s="15">
-        <v>40.5</v>
+        <v>46.082949308755</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>29</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="D24" s="14">
-        <v>233</v>
+        <v>285</v>
       </c>
       <c r="E24" s="15">
-        <v>7.725321888412</v>
+        <v>-20</v>
       </c>
       <c r="F24" s="14">
-        <v>896</v>
+        <v>916</v>
       </c>
       <c r="G24" s="14">
-        <v>892</v>
+        <v>955</v>
       </c>
       <c r="H24" s="15">
-        <v>0.448430493273</v>
+        <v>-4.083769633507</v>
       </c>
       <c r="I24" s="14">
-        <v>2476</v>
+        <v>2694</v>
       </c>
       <c r="J24" s="14">
-        <v>2417</v>
+        <v>2702</v>
       </c>
       <c r="K24" s="15">
-        <v>2.441042614811</v>
+        <v>-0.296076980014</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.769344141488</v>
+        <v>-7.613168724279</v>
       </c>
       <c r="M24" s="15">
-        <v>23.306772908366</v>
+        <v>22.957553628480</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>29</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D25" s="14">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="E25" s="15">
-        <v>-17.117117117117</v>
+        <v>-29.508196721311</v>
       </c>
       <c r="F25" s="14">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="G25" s="14">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="H25" s="15">
-        <v>-17.759562841530</v>
+        <v>-19.592875318066</v>
       </c>
       <c r="I25" s="14">
-        <v>877</v>
+        <v>964</v>
       </c>
       <c r="J25" s="14">
-        <v>965</v>
+        <v>1087</v>
       </c>
       <c r="K25" s="15">
-        <v>-9.119170984455</v>
+        <v>-11.315547378104</v>
       </c>
       <c r="L25" s="15">
-        <v>-28.055783429040</v>
+        <v>-26.299694189602</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>29</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D26" s="14">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E26" s="15">
-        <v>11.926605504587</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F26" s="14">
-        <v>454</v>
+        <v>494</v>
       </c>
       <c r="G26" s="14">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.155172413793</v>
+        <v>6.926406926406</v>
       </c>
       <c r="I26" s="14">
-        <v>1271</v>
+        <v>1403</v>
       </c>
       <c r="J26" s="14">
-        <v>1215</v>
+        <v>1323</v>
       </c>
       <c r="K26" s="15">
-        <v>4.609053497942</v>
+        <v>6.046863189720</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.346007604562</v>
+        <v>-1.750700280112</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.785942492012</v>
+        <v>-17.615971814445</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>29</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>28.571428571428</v>
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G27" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H27" s="15">
-        <v>40</v>
+        <v>52.380952380952</v>
       </c>
       <c r="I27" s="14">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="J27" s="14">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K27" s="15">
-        <v>22.972972972973</v>
+        <v>28.205128205128</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>20.481927710843</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>29</v>
@@ -1429,31 +1429,31 @@
         <v>15</v>
       </c>
       <c r="D28" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E28" s="15">
-        <v>-6.25</v>
+        <v>36.363636363636</v>
       </c>
       <c r="F28" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G28" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H28" s="15">
-        <v>11.111111111111</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="J28" s="14">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="K28" s="15">
-        <v>-5.072463768115</v>
+        <v>-3.355704697986</v>
       </c>
       <c r="L28" s="15">
-        <v>19.090909090909</v>
+        <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>29</v>
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D29" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F29" s="14">
         <v>14</v>
       </c>
       <c r="G29" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H29" s="15">
-        <v>7.692307692307</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I29" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J29" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K29" s="15">
-        <v>-17.142857142857</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="L29" s="15">
-        <v>-23.684210526315</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="M29" s="15">
-        <v>-61.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.713567839196</v>
+        <v>-92.694063926940</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,10 +1508,10 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="15">
         <v>0</v>
@@ -1520,28 +1520,28 @@
         <v>13</v>
       </c>
       <c r="G30" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H30" s="15">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J30" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K30" s="15">
-        <v>-19.354838709677</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L30" s="15">
-        <v>-26.470588235294</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="M30" s="15">
-        <v>-59.016393442622</v>
+        <v>-56.923076923076</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.297587131367</v>
+        <v>-93.103448275862</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>29</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G31" s="14">
         <v>6</v>
       </c>
       <c r="H31" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J31" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K31" s="15">
-        <v>36.363636363636</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>36.363636363636</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>29</v>
@@ -1620,19 +1620,19 @@
         <v>1</v>
       </c>
       <c r="G33" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I33" s="14">
         <v>6</v>
       </c>
       <c r="J33" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L33" s="15">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -199,61 +199,61 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,738 +851,738 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>3</v>
       </c>
       <c r="D14" s="14">
         <v>1</v>
       </c>
       <c r="E14" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F14" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G14" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H14" s="15">
-        <v>-85.714285714285</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J14" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K14" s="15">
-        <v>-72.222222222222</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="L14" s="15">
-        <v>-72.222222222222</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M14" s="15">
-        <v>-80.769230769230</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="N14" s="15">
-        <v>-95.412844036697</v>
+        <v>-93.277310924369</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>3</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F15" s="14">
         <v>21</v>
       </c>
-      <c r="C15" s="14">
-        <v>5</v>
-      </c>
-      <c r="D15" s="14">
-        <v>4</v>
-      </c>
-      <c r="E15" s="15">
-        <v>25</v>
-      </c>
-      <c r="F15" s="14">
-        <v>25</v>
-      </c>
       <c r="G15" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H15" s="15">
+        <v>50</v>
+      </c>
+      <c r="I15" s="14">
+        <v>90</v>
+      </c>
+      <c r="J15" s="14">
+        <v>63</v>
+      </c>
+      <c r="K15" s="15">
+        <v>42.857142857142</v>
+      </c>
+      <c r="L15" s="15">
         <v>66.666666666666</v>
-      </c>
-      <c r="I15" s="14">
-        <v>87</v>
-      </c>
-      <c r="J15" s="14">
-        <v>60</v>
-      </c>
-      <c r="K15" s="15">
-        <v>45</v>
-      </c>
-      <c r="L15" s="15">
-        <v>77.551020408163</v>
       </c>
       <c r="M15" s="15">
         <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>-37.857142857142</v>
+        <v>-39.597315436241</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D16" s="14">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E16" s="15">
-        <v>-14.634146341463</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F16" s="14">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G16" s="14">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="H16" s="15">
-        <v>-6.040268456375</v>
+        <v>-22.619047619047</v>
       </c>
       <c r="I16" s="14">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="J16" s="14">
-        <v>403</v>
+        <v>452</v>
       </c>
       <c r="K16" s="15">
-        <v>10.669975186104</v>
+        <v>3.761061946902</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.837370242214</v>
+        <v>-25.555555555555</v>
       </c>
       <c r="M16" s="15">
-        <v>-39.319727891156</v>
+        <v>-41.301627033792</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.382391247720</v>
+        <v>-88.771845822360</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D17" s="14">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E17" s="15">
-        <v>2.222222222222</v>
+        <v>-1.030927835051</v>
       </c>
       <c r="F17" s="14">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="G17" s="14">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="H17" s="15">
-        <v>6.918238993710</v>
+        <v>11.145510835913</v>
       </c>
       <c r="I17" s="14">
-        <v>982</v>
+        <v>1091</v>
       </c>
       <c r="J17" s="14">
-        <v>959</v>
+        <v>1056</v>
       </c>
       <c r="K17" s="15">
-        <v>2.398331595411</v>
+        <v>3.314393939393</v>
       </c>
       <c r="L17" s="15">
-        <v>4.246284501061</v>
+        <v>7.487684729064</v>
       </c>
       <c r="M17" s="15">
-        <v>43.357664233576</v>
+        <v>46.837146702557</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.769403824521</v>
+        <v>-43.733883445074</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D18" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="F18" s="14">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="G18" s="14">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H18" s="15">
-        <v>0.892857142857</v>
+        <v>-7.547169811320</v>
       </c>
       <c r="I18" s="14">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="J18" s="14">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="K18" s="15">
-        <v>4.050632911392</v>
+        <v>2.870813397129</v>
       </c>
       <c r="L18" s="15">
-        <v>-7.013574660633</v>
+        <v>-11.157024793388</v>
       </c>
       <c r="M18" s="15">
-        <v>-34.86529318542</v>
+        <v>-35.045317220543</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.300993124522</v>
+        <v>-84.975541579315</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D19" s="14">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="E19" s="15">
-        <v>5.813953488372</v>
+        <v>5.940594059405</v>
       </c>
       <c r="F19" s="14">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="G19" s="14">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.392156862745</v>
+        <v>-1.951219512195</v>
       </c>
       <c r="I19" s="14">
-        <v>1127</v>
+        <v>1234</v>
       </c>
       <c r="J19" s="14">
-        <v>1155</v>
+        <v>1256</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.424242424242</v>
+        <v>-1.751592356687</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.413354531001</v>
+        <v>-10.384894698620</v>
       </c>
       <c r="M19" s="15">
-        <v>28.068181818181</v>
+        <v>29.350104821802</v>
       </c>
       <c r="N19" s="15">
-        <v>-19.095477386934</v>
+        <v>-19.240837696335</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D20" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E20" s="15">
-        <v>20</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="F20" s="14">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G20" s="14">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="H20" s="15">
-        <v>32.941176470588</v>
+        <v>12.903225806451</v>
       </c>
       <c r="I20" s="14">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="J20" s="14">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="K20" s="15">
-        <v>6.474820143884</v>
+        <v>4.590163934426</v>
       </c>
       <c r="L20" s="15">
-        <v>-18.904109589041</v>
+        <v>-19.035532994923</v>
       </c>
       <c r="M20" s="15">
-        <v>0.338983050847</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.813915191436</v>
+        <v>-87.773093139133</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D21" s="17">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="E21" s="18">
-        <v>-0.363636363636</v>
+        <v>-10.299003322259</v>
       </c>
       <c r="F21" s="17">
+        <v>1119</v>
+      </c>
+      <c r="G21" s="17">
         <v>1118</v>
       </c>
-      <c r="G21" s="17">
-        <v>1094</v>
-      </c>
       <c r="H21" s="18">
-        <v>2.193784277879</v>
+        <v>0.089445438282</v>
       </c>
       <c r="I21" s="17">
-        <v>3354</v>
+        <v>3641</v>
       </c>
       <c r="J21" s="17">
-        <v>3268</v>
+        <v>3569</v>
       </c>
       <c r="K21" s="18">
-        <v>2.631578947368</v>
+        <v>2.017371812832</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.159912376779</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M21" s="18">
-        <v>1.329305135951</v>
+        <v>2.074572469862</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.745002437835</v>
+        <v>-72.793842935066</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="14">
+        <v>10</v>
+      </c>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>233.333333333333</v>
+      </c>
+      <c r="F22" s="14">
+        <v>24</v>
+      </c>
+      <c r="G22" s="14">
+        <v>25</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-4</v>
+      </c>
+      <c r="I22" s="14">
+        <v>81</v>
+      </c>
+      <c r="J22" s="14">
+        <v>79</v>
+      </c>
+      <c r="K22" s="15">
+        <v>2.531645569620</v>
+      </c>
+      <c r="L22" s="15">
+        <v>-4.705882352941</v>
+      </c>
+      <c r="M22" s="15">
+        <v>-28.947368421052</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="C22" s="14">
-        <v>3</v>
-      </c>
-      <c r="D22" s="14">
-        <v>9</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F22" s="14">
-        <v>18</v>
-      </c>
-      <c r="G22" s="14">
-        <v>24</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-25</v>
-      </c>
-      <c r="I22" s="14">
-        <v>71</v>
-      </c>
-      <c r="J22" s="14">
-        <v>76</v>
-      </c>
-      <c r="K22" s="15">
-        <v>-6.578947368421</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-12.345679012345</v>
-      </c>
-      <c r="M22" s="15">
-        <v>-29.702970297029</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D23" s="14">
+        <v>34</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-38.235294117647</v>
+      </c>
+      <c r="F23" s="14">
+        <v>106</v>
+      </c>
+      <c r="G23" s="14">
+        <v>98</v>
+      </c>
+      <c r="H23" s="15">
+        <v>8.163265306122</v>
+      </c>
+      <c r="I23" s="14">
+        <v>341</v>
+      </c>
+      <c r="J23" s="14">
+        <v>363</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-6.060606060606</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-11.886304909560</v>
+      </c>
+      <c r="M23" s="15">
+        <v>47.619047619047</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="E23" s="15">
-        <v>10.714285714285</v>
-      </c>
-      <c r="F23" s="14">
-        <v>109</v>
-      </c>
-      <c r="G23" s="14">
-        <v>99</v>
-      </c>
-      <c r="H23" s="15">
-        <v>10.101010101010</v>
-      </c>
-      <c r="I23" s="14">
-        <v>317</v>
-      </c>
-      <c r="J23" s="14">
-        <v>329</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-3.647416413373</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-9.686609686609</v>
-      </c>
-      <c r="M23" s="15">
-        <v>46.082949308755</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D24" s="14">
-        <v>285</v>
+        <v>239</v>
       </c>
       <c r="E24" s="15">
-        <v>-20</v>
+        <v>-8.368200836820</v>
       </c>
       <c r="F24" s="14">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="G24" s="14">
-        <v>955</v>
+        <v>971</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.083769633507</v>
+        <v>-5.252317198764</v>
       </c>
       <c r="I24" s="14">
-        <v>2694</v>
+        <v>2914</v>
       </c>
       <c r="J24" s="14">
-        <v>2702</v>
+        <v>2941</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.296076980014</v>
+        <v>-0.918055083304</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.613168724279</v>
+        <v>-6.482670089858</v>
       </c>
       <c r="M24" s="15">
-        <v>22.957553628480</v>
+        <v>23.947256486601</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D25" s="14">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="E25" s="15">
-        <v>-29.508196721311</v>
+        <v>-16.049382716049</v>
       </c>
       <c r="F25" s="14">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="G25" s="14">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="H25" s="15">
-        <v>-19.592875318066</v>
+        <v>-20.822622107969</v>
       </c>
       <c r="I25" s="14">
-        <v>964</v>
+        <v>1034</v>
       </c>
       <c r="J25" s="14">
-        <v>1087</v>
+        <v>1168</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.315547378104</v>
+        <v>-11.472602739726</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.299694189602</v>
+        <v>-26.353276353276</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D26" s="14">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="E26" s="15">
-        <v>22.222222222222</v>
+        <v>8</v>
       </c>
       <c r="F26" s="14">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="G26" s="14">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="H26" s="15">
-        <v>6.926406926406</v>
+        <v>11.587982832618</v>
       </c>
       <c r="I26" s="14">
-        <v>1403</v>
+        <v>1536</v>
       </c>
       <c r="J26" s="14">
-        <v>1323</v>
+        <v>1448</v>
       </c>
       <c r="K26" s="15">
-        <v>6.046863189720</v>
+        <v>6.077348066298</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.750700280112</v>
+        <v>-0.646830530401</v>
       </c>
       <c r="M26" s="15">
-        <v>-17.615971814445</v>
+        <v>-15.650741350906</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G27" s="14">
         <v>21</v>
       </c>
       <c r="H27" s="15">
-        <v>52.380952380952</v>
+        <v>19.047619047619</v>
       </c>
       <c r="I27" s="14">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J27" s="14">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K27" s="15">
-        <v>28.205128205128</v>
+        <v>22.619047619047</v>
       </c>
       <c r="L27" s="15">
-        <v>20.481927710843</v>
+        <v>15.730337078651</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D28" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E28" s="15">
-        <v>36.363636363636</v>
+        <v>12.5</v>
       </c>
       <c r="F28" s="14">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G28" s="14">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="H28" s="15">
-        <v>16.666666666666</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="I28" s="14">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="J28" s="14">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="K28" s="15">
-        <v>-3.355704697986</v>
+        <v>-4.848484848484</v>
       </c>
       <c r="L28" s="15">
-        <v>20</v>
+        <v>19.847328244274</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" s="15">
-        <v>-25</v>
+        <v>20</v>
       </c>
       <c r="F29" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H29" s="15">
-        <v>-6.666666666666</v>
+        <v>17.647058823529</v>
       </c>
       <c r="I29" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J29" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K29" s="15">
-        <v>-17.948717948717</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="L29" s="15">
-        <v>-21.951219512195</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="M29" s="15">
-        <v>-60</v>
+        <v>-58.241758241758</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.694063926940</v>
+        <v>-91.949152542372</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="14">
         <v>3</v>
       </c>
       <c r="E30" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F30" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G30" s="14">
         <v>13</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I30" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J30" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K30" s="15">
-        <v>-17.647058823529</v>
+        <v>-13.513513513513</v>
       </c>
       <c r="L30" s="15">
-        <v>-24.324324324324</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="M30" s="15">
-        <v>-56.923076923076</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.103448275862</v>
+        <v>-92.677345537757</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="D31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" s="15">
         <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H31" s="15">
         <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J31" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K31" s="15">
-        <v>33.333333333333</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>14.285714285714</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,22 +1608,22 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F33" s="14">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="G33" s="14">
         <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>6</v>
@@ -1635,13 +1635,13 @@
         <v>-14.285714285714</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>708</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>20509</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>9978</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>14993</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>8788</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>12552</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>68033</v>

--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -852,40 +852,40 @@
         <v>19</v>
       </c>
       <c r="C14" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="14">
         <v>1</v>
       </c>
       <c r="E14" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="14">
         <v>4</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I14" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J14" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K14" s="15">
-        <v>-57.894736842105</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="15">
-        <v>-73.333333333333</v>
+        <v>-68.75</v>
       </c>
       <c r="N14" s="15">
-        <v>-93.277310924369</v>
+        <v>-92.366412213740</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-33.333333333333</v>
+        <v>400</v>
       </c>
       <c r="F15" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J15" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K15" s="15">
-        <v>42.857142857142</v>
+        <v>46.875</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>51.612903225806</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>51.612903225806</v>
       </c>
       <c r="N15" s="15">
-        <v>-39.597315436241</v>
+        <v>-42.682926829268</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D16" s="14">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E16" s="15">
-        <v>-57.142857142857</v>
+        <v>10.344827586206</v>
       </c>
       <c r="F16" s="14">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G16" s="14">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H16" s="15">
-        <v>-22.619047619047</v>
+        <v>-22.839506172839</v>
       </c>
       <c r="I16" s="14">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="J16" s="14">
-        <v>452</v>
+        <v>481</v>
       </c>
       <c r="K16" s="15">
-        <v>3.761061946902</v>
+        <v>4.573804573804</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.555555555555</v>
+        <v>-25.260029717682</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.301627033792</v>
+        <v>-41.169590643274</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.771845822360</v>
+        <v>-88.737124944021</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D17" s="14">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="E17" s="15">
-        <v>-1.030927835051</v>
+        <v>15.151515151515</v>
       </c>
       <c r="F17" s="14">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G17" s="14">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H17" s="15">
-        <v>11.145510835913</v>
+        <v>10.153846153846</v>
       </c>
       <c r="I17" s="14">
-        <v>1091</v>
+        <v>1172</v>
       </c>
       <c r="J17" s="14">
-        <v>1056</v>
+        <v>1122</v>
       </c>
       <c r="K17" s="15">
-        <v>3.314393939393</v>
+        <v>4.456327985739</v>
       </c>
       <c r="L17" s="15">
-        <v>7.487684729064</v>
+        <v>6.352087114337</v>
       </c>
       <c r="M17" s="15">
-        <v>46.837146702557</v>
+        <v>41.717049576783</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.733883445074</v>
+        <v>-44.690891930155</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D18" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E18" s="15">
-        <v>-21.739130434782</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F18" s="14">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G18" s="14">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H18" s="15">
-        <v>-7.547169811320</v>
+        <v>-7.070707070707</v>
       </c>
       <c r="I18" s="14">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="J18" s="14">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="K18" s="15">
-        <v>2.870813397129</v>
+        <v>2.702702702702</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.157024793388</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M18" s="15">
-        <v>-35.045317220543</v>
+        <v>-35.410764872521</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.975541579315</v>
+        <v>-85.261797026502</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>107</v>
       </c>
       <c r="D19" s="14">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E19" s="15">
-        <v>5.940594059405</v>
+        <v>11.458333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G19" s="14">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="H19" s="15">
-        <v>-1.951219512195</v>
+        <v>0.251256281407</v>
       </c>
       <c r="I19" s="14">
-        <v>1234</v>
+        <v>1337</v>
       </c>
       <c r="J19" s="14">
-        <v>1256</v>
+        <v>1353</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.751592356687</v>
+        <v>-1.182557280118</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.384894698620</v>
+        <v>-8.923705722070</v>
       </c>
       <c r="M19" s="15">
-        <v>29.350104821802</v>
+        <v>28.065134099616</v>
       </c>
       <c r="N19" s="15">
-        <v>-19.240837696335</v>
+        <v>-18.772782503037</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>23</v>
       </c>
       <c r="D20" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E20" s="15">
-        <v>-14.814814814814</v>
+        <v>-28.125</v>
       </c>
       <c r="F20" s="14">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G20" s="14">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="H20" s="15">
-        <v>12.903225806451</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="J20" s="14">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="K20" s="15">
-        <v>4.590163934426</v>
+        <v>1.479289940828</v>
       </c>
       <c r="L20" s="15">
-        <v>-19.035532994923</v>
+        <v>-18.912529550827</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>-0.290697674418</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.773093139133</v>
+        <v>-87.612856626941</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D21" s="17">
-        <v>301</v>
+        <v>251</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.299003322259</v>
+        <v>7.171314741035</v>
       </c>
       <c r="F21" s="17">
-        <v>1119</v>
+        <v>1103</v>
       </c>
       <c r="G21" s="17">
-        <v>1118</v>
+        <v>1104</v>
       </c>
       <c r="H21" s="18">
-        <v>0.089445438282</v>
+        <v>-0.090579710144</v>
       </c>
       <c r="I21" s="17">
-        <v>3641</v>
+        <v>3915</v>
       </c>
       <c r="J21" s="17">
-        <v>3569</v>
+        <v>3822</v>
       </c>
       <c r="K21" s="18">
-        <v>2.017371812832</v>
+        <v>2.433281004709</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.333333333333</v>
+        <v>-8.442469597754</v>
       </c>
       <c r="M21" s="18">
-        <v>2.074572469862</v>
+        <v>1.162790697674</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.793842935066</v>
+        <v>-72.791715894085</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E22" s="15">
-        <v>233.333333333333</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F22" s="14">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G22" s="14">
         <v>25</v>
       </c>
       <c r="H22" s="15">
-        <v>-4</v>
+        <v>28</v>
       </c>
       <c r="I22" s="14">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J22" s="14">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K22" s="15">
-        <v>2.531645569620</v>
+        <v>10.588235294117</v>
       </c>
       <c r="L22" s="15">
-        <v>-4.705882352941</v>
+        <v>5.617977528089</v>
       </c>
       <c r="M22" s="15">
-        <v>-28.947368421052</v>
+        <v>-23.577235772357</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>28</v>
@@ -1221,37 +1221,37 @@
         <v>29</v>
       </c>
       <c r="C23" s="14">
+        <v>26</v>
+      </c>
+      <c r="D23" s="14">
         <v>21</v>
       </c>
-      <c r="D23" s="14">
-        <v>34</v>
-      </c>
       <c r="E23" s="15">
-        <v>-38.235294117647</v>
+        <v>23.809523809523</v>
       </c>
       <c r="F23" s="14">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G23" s="14">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H23" s="15">
-        <v>8.163265306122</v>
+        <v>-2</v>
       </c>
       <c r="I23" s="14">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="J23" s="14">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="K23" s="15">
-        <v>-6.060606060606</v>
+        <v>-4.427083333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.886304909560</v>
+        <v>-12.826603325415</v>
       </c>
       <c r="M23" s="15">
-        <v>47.619047619047</v>
+        <v>41.698841698841</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>28</v>
@@ -1262,37 +1262,37 @@
         <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>219</v>
+        <v>264</v>
       </c>
       <c r="D24" s="14">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E24" s="15">
-        <v>-8.368200836820</v>
+        <v>8.196721311475</v>
       </c>
       <c r="F24" s="14">
-        <v>920</v>
+        <v>964</v>
       </c>
       <c r="G24" s="14">
-        <v>971</v>
+        <v>1000</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.252317198764</v>
+        <v>-3.6</v>
       </c>
       <c r="I24" s="14">
-        <v>2914</v>
+        <v>3176</v>
       </c>
       <c r="J24" s="14">
-        <v>2941</v>
+        <v>3184</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.918055083304</v>
+        <v>-0.251256281407</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.482670089858</v>
+        <v>-3.874092009685</v>
       </c>
       <c r="M24" s="15">
-        <v>23.947256486601</v>
+        <v>25.335438042620</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>28</v>
@@ -1303,34 +1303,34 @@
         <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D25" s="14">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E25" s="15">
-        <v>-16.049382716049</v>
+        <v>-4.395604395604</v>
       </c>
       <c r="F25" s="14">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="G25" s="14">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="H25" s="15">
-        <v>-20.822622107969</v>
+        <v>-16.543209876543</v>
       </c>
       <c r="I25" s="14">
-        <v>1034</v>
+        <v>1122</v>
       </c>
       <c r="J25" s="14">
-        <v>1168</v>
+        <v>1259</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.472602739726</v>
+        <v>-10.881652104845</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.353276353276</v>
+        <v>-24.444444444444</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>28</v>
@@ -1344,37 +1344,37 @@
         <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="D26" s="14">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E26" s="15">
-        <v>8</v>
+        <v>-14.516129032258</v>
       </c>
       <c r="F26" s="14">
-        <v>520</v>
+        <v>496</v>
       </c>
       <c r="G26" s="14">
         <v>466</v>
       </c>
       <c r="H26" s="15">
-        <v>11.587982832618</v>
+        <v>6.437768240343</v>
       </c>
       <c r="I26" s="14">
-        <v>1536</v>
+        <v>1641</v>
       </c>
       <c r="J26" s="14">
-        <v>1448</v>
+        <v>1572</v>
       </c>
       <c r="K26" s="15">
-        <v>6.077348066298</v>
+        <v>4.389312977099</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.646830530401</v>
+        <v>-0.303766707168</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.650741350906</v>
+        <v>-17.908954477238</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>28</v>
@@ -1385,34 +1385,34 @@
         <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D27" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F27" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G27" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H27" s="15">
-        <v>19.047619047619</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I27" s="14">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="J27" s="14">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K27" s="15">
-        <v>22.619047619047</v>
+        <v>26.744186046511</v>
       </c>
       <c r="L27" s="15">
-        <v>15.730337078651</v>
+        <v>9</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>28</v>
@@ -1426,34 +1426,34 @@
         <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D28" s="14">
         <v>16</v>
       </c>
       <c r="E28" s="15">
-        <v>12.5</v>
+        <v>-25</v>
       </c>
       <c r="F28" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G28" s="14">
         <v>59</v>
       </c>
       <c r="H28" s="15">
-        <v>-6.779661016949</v>
+        <v>-1.694915254237</v>
       </c>
       <c r="I28" s="14">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="J28" s="14">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="K28" s="15">
-        <v>-4.848484848484</v>
+        <v>-7.734806629834</v>
       </c>
       <c r="L28" s="15">
-        <v>19.847328244274</v>
+        <v>15.972222222222</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>28</v>
@@ -1467,40 +1467,40 @@
         <v>35</v>
       </c>
       <c r="C29" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D29" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G29" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H29" s="15">
-        <v>17.647058823529</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J29" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K29" s="15">
-        <v>-13.636363636363</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L29" s="15">
-        <v>-11.627906976744</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="M29" s="15">
-        <v>-58.241758241758</v>
+        <v>-65.217391304347</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.949152542372</v>
+        <v>-92.248062015503</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,40 +1508,40 @@
         <v>36</v>
       </c>
       <c r="C30" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G30" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H30" s="15">
-        <v>30.769230769230</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I30" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J30" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K30" s="15">
-        <v>-13.513513513513</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="L30" s="15">
-        <v>-17.948717948717</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M30" s="15">
-        <v>-55.555555555555</v>
+        <v>-60.919540229885</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.677345537757</v>
+        <v>-92.827004219409</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,31 +1552,31 @@
         <v>38</v>
       </c>
       <c r="D31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="15">
         <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I31" s="14">
         <v>17</v>
       </c>
       <c r="J31" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K31" s="15">
-        <v>13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L31" s="15">
-        <v>21.428571428571</v>
+        <v>6.25</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>28</v>

--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,12 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -223,9 +229,6 @@
     <t>Transit</t>
   </si>
   <si>
-    <t>***.*</t>
-  </si>
-  <si>
     <t>Housing</t>
   </si>
   <si>
@@ -251,9 +254,6 @@
   </si>
   <si>
     <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,23 +851,23 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>2</v>
-      </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>100</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>5</v>
       </c>
       <c r="G14" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" s="15">
-        <v>25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I14" s="14">
         <v>10</v>
@@ -879,633 +879,633 @@
         <v>-50</v>
       </c>
       <c r="L14" s="15">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M14" s="15">
-        <v>-68.75</v>
+        <v>-73.684210526315</v>
       </c>
       <c r="N14" s="15">
-        <v>-92.366412213740</v>
+        <v>-92.647058823529</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>5</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E15" s="15">
-        <v>400</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F15" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G15" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H15" s="15">
-        <v>66.666666666666</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J15" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K15" s="15">
-        <v>46.875</v>
+        <v>39.436619718309</v>
       </c>
       <c r="L15" s="15">
-        <v>51.612903225806</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>51.612903225806</v>
+        <v>43.478260869565</v>
       </c>
       <c r="N15" s="15">
-        <v>-42.682926829268</v>
+        <v>-44.067796610169</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D16" s="14">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E16" s="15">
-        <v>10.344827586206</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="F16" s="14">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G16" s="14">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H16" s="15">
-        <v>-22.839506172839</v>
+        <v>-18.589743589743</v>
       </c>
       <c r="I16" s="14">
-        <v>503</v>
+        <v>538</v>
       </c>
       <c r="J16" s="14">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="K16" s="15">
-        <v>4.573804573804</v>
+        <v>3.861003861003</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.260029717682</v>
+        <v>-24.649859943977</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.169590643274</v>
+        <v>-41.330425299890</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.737124944021</v>
+        <v>-88.711707931179</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D17" s="14">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="E17" s="15">
-        <v>15.151515151515</v>
+        <v>-12.087912087912</v>
       </c>
       <c r="F17" s="14">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G17" s="14">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="H17" s="15">
-        <v>10.153846153846</v>
+        <v>4.360465116279</v>
       </c>
       <c r="I17" s="14">
-        <v>1172</v>
+        <v>1255</v>
       </c>
       <c r="J17" s="14">
-        <v>1122</v>
+        <v>1213</v>
       </c>
       <c r="K17" s="15">
-        <v>4.456327985739</v>
+        <v>3.462489694971</v>
       </c>
       <c r="L17" s="15">
-        <v>6.352087114337</v>
+        <v>5.373635600335</v>
       </c>
       <c r="M17" s="15">
-        <v>41.717049576783</v>
+        <v>40.223463687150</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.690891930155</v>
+        <v>-45.100612423447</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D18" s="14">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E18" s="15">
-        <v>-7.692307692307</v>
+        <v>-64.102564102564</v>
       </c>
       <c r="F18" s="14">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G18" s="14">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="H18" s="15">
-        <v>-7.070707070707</v>
+        <v>-30.172413793103</v>
       </c>
       <c r="I18" s="14">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="J18" s="14">
-        <v>444</v>
+        <v>483</v>
       </c>
       <c r="K18" s="15">
-        <v>2.702702702702</v>
+        <v>-3.105590062111</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.636363636363</v>
+        <v>-15.978456014362</v>
       </c>
       <c r="M18" s="15">
-        <v>-35.410764872521</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.261797026502</v>
+        <v>-86.008968609865</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D19" s="14">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E19" s="15">
-        <v>11.458333333333</v>
+        <v>1.010101010101</v>
       </c>
       <c r="F19" s="14">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G19" s="14">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="H19" s="15">
-        <v>0.251256281407</v>
+        <v>4.166666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>1337</v>
+        <v>1434</v>
       </c>
       <c r="J19" s="14">
-        <v>1353</v>
+        <v>1453</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.182557280118</v>
+        <v>-1.307639366827</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.923705722070</v>
+        <v>-7.662588538312</v>
       </c>
       <c r="M19" s="15">
-        <v>28.065134099616</v>
+        <v>29.656419529837</v>
       </c>
       <c r="N19" s="15">
-        <v>-18.772782503037</v>
+        <v>-19.302194710185</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D20" s="14">
         <v>32</v>
       </c>
       <c r="E20" s="15">
-        <v>-28.125</v>
+        <v>-18.75</v>
       </c>
       <c r="F20" s="14">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G20" s="14">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="I20" s="14">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="J20" s="14">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="K20" s="15">
-        <v>1.479289940828</v>
+        <v>-0.540540540540</v>
       </c>
       <c r="L20" s="15">
-        <v>-18.912529550827</v>
+        <v>-19.650655021834</v>
       </c>
       <c r="M20" s="15">
-        <v>-0.290697674418</v>
+        <v>-2.645502645502</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.612856626941</v>
+        <v>-87.617765814266</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="D21" s="17">
-        <v>251</v>
+        <v>305</v>
       </c>
       <c r="E21" s="18">
-        <v>7.171314741035</v>
+        <v>-14.754098360655</v>
       </c>
       <c r="F21" s="17">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="G21" s="17">
-        <v>1104</v>
+        <v>1135</v>
       </c>
       <c r="H21" s="18">
-        <v>-0.090579710144</v>
+        <v>-3.876651982378</v>
       </c>
       <c r="I21" s="17">
-        <v>3915</v>
+        <v>4172</v>
       </c>
       <c r="J21" s="17">
-        <v>3822</v>
+        <v>4128</v>
       </c>
       <c r="K21" s="18">
-        <v>2.433281004709</v>
+        <v>1.065891472868</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.442469597754</v>
+        <v>-8.528831396623</v>
       </c>
       <c r="M21" s="18">
-        <v>1.162790697674</v>
+        <v>0.312575138254</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.791715894085</v>
+        <v>-73.012484636781</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" s="15">
-        <v>116.666666666667</v>
+        <v>60</v>
       </c>
       <c r="F22" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G22" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H22" s="15">
-        <v>28</v>
+        <v>43.478260869565</v>
       </c>
       <c r="I22" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="J22" s="14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K22" s="15">
-        <v>10.588235294117</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>5.617977528089</v>
+        <v>6.25</v>
       </c>
       <c r="M22" s="15">
-        <v>-23.577235772357</v>
+        <v>-20.3125</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D23" s="14">
+        <v>27</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-29.629629629629</v>
+      </c>
+      <c r="F23" s="14">
+        <v>97</v>
+      </c>
+      <c r="G23" s="14">
+        <v>110</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-11.818181818181</v>
+      </c>
+      <c r="I23" s="14">
+        <v>385</v>
+      </c>
+      <c r="J23" s="14">
+        <v>411</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-6.326034063260</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-12.698412698412</v>
+      </c>
+      <c r="M23" s="15">
+        <v>38.989169675090</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>21</v>
-      </c>
-      <c r="E23" s="15">
-        <v>23.809523809523</v>
-      </c>
-      <c r="F23" s="14">
-        <v>98</v>
-      </c>
-      <c r="G23" s="14">
-        <v>100</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-2</v>
-      </c>
-      <c r="I23" s="14">
-        <v>367</v>
-      </c>
-      <c r="J23" s="14">
-        <v>384</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-4.427083333333</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-12.826603325415</v>
-      </c>
-      <c r="M23" s="15">
-        <v>41.698841698841</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>264</v>
+        <v>208</v>
       </c>
       <c r="D24" s="14">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E24" s="15">
-        <v>8.196721311475</v>
+        <v>-17.131474103585</v>
       </c>
       <c r="F24" s="14">
-        <v>964</v>
+        <v>921</v>
       </c>
       <c r="G24" s="14">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.6</v>
+        <v>-9.528487229862</v>
       </c>
       <c r="I24" s="14">
-        <v>3176</v>
+        <v>3385</v>
       </c>
       <c r="J24" s="14">
-        <v>3184</v>
+        <v>3435</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.251256281407</v>
+        <v>-1.455604075691</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.874092009685</v>
+        <v>-4.189074440985</v>
       </c>
       <c r="M24" s="15">
-        <v>25.335438042620</v>
+        <v>24.677716390423</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D25" s="14">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E25" s="15">
-        <v>-4.395604395604</v>
+        <v>-28</v>
       </c>
       <c r="F25" s="14">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="G25" s="14">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="H25" s="15">
-        <v>-16.543209876543</v>
+        <v>-19.289340101522</v>
       </c>
       <c r="I25" s="14">
-        <v>1122</v>
+        <v>1195</v>
       </c>
       <c r="J25" s="14">
-        <v>1259</v>
+        <v>1359</v>
       </c>
       <c r="K25" s="15">
-        <v>-10.881652104845</v>
+        <v>-12.067696835908</v>
       </c>
       <c r="L25" s="15">
-        <v>-24.444444444444</v>
+        <v>-24.414927261227</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="D26" s="14">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="E26" s="15">
-        <v>-14.516129032258</v>
+        <v>53.061224489795</v>
       </c>
       <c r="F26" s="14">
-        <v>496</v>
+        <v>520</v>
       </c>
       <c r="G26" s="14">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="H26" s="15">
-        <v>6.437768240343</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>1641</v>
+        <v>1789</v>
       </c>
       <c r="J26" s="14">
-        <v>1572</v>
+        <v>1670</v>
       </c>
       <c r="K26" s="15">
-        <v>4.389312977099</v>
+        <v>7.125748502994</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.303766707168</v>
+        <v>0.959367945823</v>
       </c>
       <c r="M26" s="15">
-        <v>-17.908954477238</v>
+        <v>-15.533522190746</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E27" s="15">
-        <v>200</v>
+        <v>12.5</v>
       </c>
       <c r="F27" s="14">
         <v>23</v>
       </c>
       <c r="G27" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H27" s="15">
-        <v>21.052631578947</v>
+        <v>15</v>
       </c>
       <c r="I27" s="14">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J27" s="14">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="K27" s="15">
-        <v>26.744186046511</v>
+        <v>25.531914893617</v>
       </c>
       <c r="L27" s="15">
-        <v>9</v>
+        <v>12.380952380952</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D28" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E28" s="15">
-        <v>-25</v>
+        <v>61.538461538461</v>
       </c>
       <c r="F28" s="14">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G28" s="14">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H28" s="15">
-        <v>-1.694915254237</v>
+        <v>12.5</v>
       </c>
       <c r="I28" s="14">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="J28" s="14">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K28" s="15">
-        <v>-7.734806629834</v>
+        <v>-3.626943005181</v>
       </c>
       <c r="L28" s="15">
-        <v>15.972222222222</v>
+        <v>16.981132075471</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" s="14">
         <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F29" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G29" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I29" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J29" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K29" s="15">
-        <v>-13.043478260869</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-14.893617021276</v>
+        <v>-12.244897959183</v>
       </c>
       <c r="M29" s="15">
-        <v>-65.217391304347</v>
+        <v>-67.424242424242</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.248062015503</v>
+        <v>-92.138939670932</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="14">
         <v>2</v>
@@ -1517,42 +1517,42 @@
         <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G30" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H30" s="15">
-        <v>8.333333333333</v>
+        <v>10</v>
       </c>
       <c r="I30" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J30" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K30" s="15">
-        <v>-12.820512820512</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="L30" s="15">
-        <v>-19.047619047619</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M30" s="15">
-        <v>-60.919540229885</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.827004219409</v>
+        <v>-92.8</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E31" s="15">
         <v>-100</v>
@@ -1561,28 +1561,28 @@
         <v>2</v>
       </c>
       <c r="G31" s="14">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H31" s="15">
-        <v>-66.666666666666</v>
+        <v>-87.5</v>
       </c>
       <c r="I31" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J31" s="14">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>6.25</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,41 +1607,41 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>38</v>
+      <c r="C33" s="14">
+        <v>1</v>
+      </c>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>0</v>
+      </c>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="14">
         <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I33" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K33" s="15">
-        <v>-14.285714285714</v>
+        <v>-12.5</v>
       </c>
       <c r="L33" s="15">
-        <v>-14.285714285714</v>
+        <v>-12.5</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>708</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>20509</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>9978</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>14993</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>8788</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>12552</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>68033</v>

--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>2</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,31 +861,31 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G14" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>66.666666666666</v>
+        <v>250</v>
       </c>
       <c r="I14" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J14" s="14">
         <v>20</v>
       </c>
       <c r="K14" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="L14" s="15">
-        <v>-54.545454545454</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="M14" s="15">
-        <v>-73.684210526315</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="N14" s="15">
-        <v>-92.647058823529</v>
+        <v>-91.724137931034</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>-28.571428571428</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G15" s="14">
         <v>15</v>
       </c>
       <c r="H15" s="15">
-        <v>13.333333333333</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J15" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K15" s="15">
-        <v>39.436619718309</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>40.845070422535</v>
       </c>
       <c r="M15" s="15">
-        <v>43.478260869565</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-44.067796610169</v>
+        <v>-46.808510638297</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D16" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E16" s="15">
-        <v>-5.405405405405</v>
+        <v>8.823529411764</v>
       </c>
       <c r="F16" s="14">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G16" s="14">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H16" s="15">
-        <v>-18.589743589743</v>
+        <v>-13.422818791946</v>
       </c>
       <c r="I16" s="14">
-        <v>538</v>
+        <v>579</v>
       </c>
       <c r="J16" s="14">
-        <v>518</v>
+        <v>552</v>
       </c>
       <c r="K16" s="15">
-        <v>3.861003861003</v>
+        <v>4.891304347826</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.649859943977</v>
+        <v>-22.8</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.330425299890</v>
+        <v>-40.615384615384</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.711707931179</v>
+        <v>-88.568608094768</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D17" s="14">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="E17" s="15">
-        <v>-12.087912087912</v>
+        <v>-46.280991735537</v>
       </c>
       <c r="F17" s="14">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="G17" s="14">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="H17" s="15">
-        <v>4.360465116279</v>
+        <v>-12.266666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>1255</v>
+        <v>1328</v>
       </c>
       <c r="J17" s="14">
-        <v>1213</v>
+        <v>1334</v>
       </c>
       <c r="K17" s="15">
-        <v>3.462489694971</v>
+        <v>-0.449775112443</v>
       </c>
       <c r="L17" s="15">
-        <v>5.373635600335</v>
+        <v>3.912363067292</v>
       </c>
       <c r="M17" s="15">
-        <v>40.223463687150</v>
+        <v>38.622129436325</v>
       </c>
       <c r="N17" s="15">
-        <v>-45.100612423447</v>
+        <v>-45.662847790507</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E18" s="15">
-        <v>-64.102564102564</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F18" s="14">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G18" s="14">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H18" s="15">
-        <v>-30.172413793103</v>
+        <v>-38.211382113821</v>
       </c>
       <c r="I18" s="14">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="J18" s="14">
-        <v>483</v>
+        <v>518</v>
       </c>
       <c r="K18" s="15">
-        <v>-3.105590062111</v>
+        <v>-5.598455598455</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.978456014362</v>
+        <v>-17.676767676767</v>
       </c>
       <c r="M18" s="15">
-        <v>-38.095238095238</v>
+        <v>-40.073529411764</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.008968609865</v>
+        <v>-86.390203172836</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D19" s="14">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E19" s="15">
-        <v>1.010101010101</v>
+        <v>-14.018691588785</v>
       </c>
       <c r="F19" s="14">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="G19" s="14">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="H19" s="15">
-        <v>4.166666666666</v>
+        <v>0.493827160493</v>
       </c>
       <c r="I19" s="14">
-        <v>1434</v>
+        <v>1536</v>
       </c>
       <c r="J19" s="14">
-        <v>1453</v>
+        <v>1560</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.307639366827</v>
+        <v>-1.538461538461</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.662588538312</v>
+        <v>-6.398537477148</v>
       </c>
       <c r="M19" s="15">
-        <v>29.656419529837</v>
+        <v>31.058020477815</v>
       </c>
       <c r="N19" s="15">
-        <v>-19.302194710185</v>
+        <v>-19.454640797063</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D20" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E20" s="15">
-        <v>-18.75</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="F20" s="14">
         <v>102</v>
       </c>
       <c r="G20" s="14">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="H20" s="15">
-        <v>-12.820512820512</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I20" s="14">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="J20" s="14">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="K20" s="15">
-        <v>-0.540540540540</v>
+        <v>-1.237623762376</v>
       </c>
       <c r="L20" s="15">
-        <v>-19.650655021834</v>
+        <v>-18.404907975460</v>
       </c>
       <c r="M20" s="15">
-        <v>-2.645502645502</v>
+        <v>-3.155339805825</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.617765814266</v>
+        <v>-87.345385347288</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="D21" s="17">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.754098360655</v>
+        <v>-26.268656716417</v>
       </c>
       <c r="F21" s="17">
-        <v>1091</v>
+        <v>1063</v>
       </c>
       <c r="G21" s="17">
-        <v>1135</v>
+        <v>1195</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.876651982378</v>
+        <v>-11.046025104602</v>
       </c>
       <c r="I21" s="17">
-        <v>4172</v>
+        <v>4443</v>
       </c>
       <c r="J21" s="17">
-        <v>4128</v>
+        <v>4463</v>
       </c>
       <c r="K21" s="18">
-        <v>1.065891472868</v>
+        <v>-0.448129061169</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.528831396623</v>
+        <v>-8.316137020222</v>
       </c>
       <c r="M21" s="18">
-        <v>0.312575138254</v>
+        <v>-0.089948279739</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.012484636781</v>
+        <v>-73.064565019702</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>3</v>
+      </c>
+      <c r="D22" s="14">
         <v>8</v>
       </c>
-      <c r="D22" s="14">
-        <v>5</v>
-      </c>
       <c r="E22" s="15">
-        <v>60</v>
+        <v>-62.5</v>
       </c>
       <c r="F22" s="14">
         <v>33</v>
       </c>
       <c r="G22" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H22" s="15">
-        <v>43.478260869565</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J22" s="14">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K22" s="15">
-        <v>13.333333333333</v>
+        <v>8.163265306122</v>
       </c>
       <c r="L22" s="15">
-        <v>6.25</v>
+        <v>9.278350515463</v>
       </c>
       <c r="M22" s="15">
-        <v>-20.3125</v>
+        <v>-19.083969465648</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D23" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E23" s="15">
-        <v>-29.629629629629</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="F23" s="14">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G23" s="14">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H23" s="15">
-        <v>-11.818181818181</v>
+        <v>-21.238938053097</v>
       </c>
       <c r="I23" s="14">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="J23" s="14">
-        <v>411</v>
+        <v>442</v>
       </c>
       <c r="K23" s="15">
-        <v>-6.326034063260</v>
+        <v>-7.466063348416</v>
       </c>
       <c r="L23" s="15">
-        <v>-12.698412698412</v>
+        <v>-13.713080168776</v>
       </c>
       <c r="M23" s="15">
-        <v>38.989169675090</v>
+        <v>36.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="D24" s="14">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="E24" s="15">
-        <v>-17.131474103585</v>
+        <v>4.932735426008</v>
       </c>
       <c r="F24" s="14">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="G24" s="14">
-        <v>1018</v>
+        <v>956</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.528487229862</v>
+        <v>-3.451882845188</v>
       </c>
       <c r="I24" s="14">
-        <v>3385</v>
+        <v>3614</v>
       </c>
       <c r="J24" s="14">
-        <v>3435</v>
+        <v>3658</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.455604075691</v>
+        <v>-1.202843083652</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.189074440985</v>
+        <v>-3.652359370834</v>
       </c>
       <c r="M24" s="15">
-        <v>24.677716390423</v>
+        <v>24.277854195323</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D25" s="14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E25" s="15">
-        <v>-28</v>
+        <v>-14.736842105263</v>
       </c>
       <c r="F25" s="14">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G25" s="14">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="H25" s="15">
-        <v>-19.289340101522</v>
+        <v>-13.896457765667</v>
       </c>
       <c r="I25" s="14">
-        <v>1195</v>
+        <v>1280</v>
       </c>
       <c r="J25" s="14">
-        <v>1359</v>
+        <v>1454</v>
       </c>
       <c r="K25" s="15">
-        <v>-12.067696835908</v>
+        <v>-11.966987620357</v>
       </c>
       <c r="L25" s="15">
-        <v>-24.414927261227</v>
+        <v>-23.353293413173</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="D26" s="14">
-        <v>98</v>
+        <v>161</v>
       </c>
       <c r="E26" s="15">
-        <v>53.061224489795</v>
+        <v>-20.496894409937</v>
       </c>
       <c r="F26" s="14">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="G26" s="14">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="H26" s="15">
-        <v>14.285714285714</v>
+        <v>0.787401574803</v>
       </c>
       <c r="I26" s="14">
-        <v>1789</v>
+        <v>1910</v>
       </c>
       <c r="J26" s="14">
-        <v>1670</v>
+        <v>1831</v>
       </c>
       <c r="K26" s="15">
-        <v>7.125748502994</v>
+        <v>4.314582195521</v>
       </c>
       <c r="L26" s="15">
-        <v>0.959367945823</v>
+        <v>1.272534464475</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.533522190746</v>
+        <v>-16.484477481416</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E27" s="15">
-        <v>12.5</v>
+        <v>-60</v>
       </c>
       <c r="F27" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G27" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H27" s="15">
-        <v>15</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I27" s="14">
         <v>118</v>
       </c>
       <c r="J27" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K27" s="15">
-        <v>25.531914893617</v>
+        <v>19.191919191919</v>
       </c>
       <c r="L27" s="15">
-        <v>12.380952380952</v>
+        <v>6.306306306306</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D28" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E28" s="15">
-        <v>61.538461538461</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F28" s="14">
         <v>63</v>
       </c>
       <c r="G28" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H28" s="15">
-        <v>12.5</v>
+        <v>1.612903225806</v>
       </c>
       <c r="I28" s="14">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="J28" s="14">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="K28" s="15">
-        <v>-3.626943005181</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="L28" s="15">
-        <v>16.981132075471</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E29" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F29" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H29" s="15">
-        <v>7.692307692307</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I29" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J29" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K29" s="15">
-        <v>-10.416666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-12.244897959183</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M29" s="15">
-        <v>-67.424242424242</v>
+        <v>-67.391304347826</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.138939670932</v>
+        <v>-92.320819112628</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1511,72 +1511,72 @@
         <v>2</v>
       </c>
       <c r="D30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F30" s="14">
+        <v>10</v>
+      </c>
+      <c r="G30" s="14">
         <v>11</v>
       </c>
-      <c r="G30" s="14">
-        <v>10</v>
-      </c>
       <c r="H30" s="15">
-        <v>10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I30" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J30" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K30" s="15">
-        <v>-12.195121951219</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="L30" s="15">
-        <v>-18.181818181818</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="M30" s="15">
-        <v>-63.636363636363</v>
+        <v>-63.106796116504</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.8</v>
+        <v>-92.923649906890</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>4</v>
       </c>
       <c r="D31" s="14">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E31" s="15">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G31" s="14">
         <v>16</v>
       </c>
       <c r="H31" s="15">
-        <v>-87.5</v>
+        <v>-62.5</v>
       </c>
       <c r="I31" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J31" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K31" s="15">
-        <v>-33.333333333333</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="L31" s="15">
-        <v>-5.263157894736</v>
+        <v>15</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,23 +1607,23 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
-      </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>0</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
         <v>7</v>
@@ -1635,7 +1635,7 @@
         <v>-12.5</v>
       </c>
       <c r="L33" s="15">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -851,369 +851,369 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>2</v>
-      </c>
-      <c r="D14" s="13" t="s">
+      <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G14" s="14">
         <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="I14" s="14">
         <v>12</v>
       </c>
       <c r="J14" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K14" s="15">
-        <v>-40</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L14" s="15">
-        <v>-47.826086956521</v>
+        <v>-52</v>
       </c>
       <c r="M14" s="15">
         <v>-69.230769230769</v>
       </c>
       <c r="N14" s="15">
-        <v>-91.724137931034</v>
+        <v>-92.105263157894</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
         <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E15" s="15">
-        <v>-50</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F15" s="14">
         <v>13</v>
       </c>
       <c r="G15" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H15" s="15">
-        <v>-13.333333333333</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I15" s="14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J15" s="14">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>24.390243902439</v>
       </c>
       <c r="L15" s="15">
-        <v>40.845070422535</v>
+        <v>30.769230769230</v>
       </c>
       <c r="M15" s="15">
-        <v>33.333333333333</v>
+        <v>32.467532467532</v>
       </c>
       <c r="N15" s="15">
-        <v>-46.808510638297</v>
+        <v>-49.753694581280</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="14">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E16" s="15">
-        <v>8.823529411764</v>
+        <v>-25.490196078431</v>
       </c>
       <c r="F16" s="14">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="G16" s="14">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H16" s="15">
-        <v>-13.422818791946</v>
+        <v>-3.973509933774</v>
       </c>
       <c r="I16" s="14">
-        <v>579</v>
+        <v>619</v>
       </c>
       <c r="J16" s="14">
-        <v>552</v>
+        <v>603</v>
       </c>
       <c r="K16" s="15">
-        <v>4.891304347826</v>
+        <v>2.653399668325</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.8</v>
+        <v>-22.625</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.615384615384</v>
+        <v>-41.215574548907</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.568608094768</v>
+        <v>-88.524286243974</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D17" s="14">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E17" s="15">
-        <v>-46.280991735537</v>
+        <v>-23.853211009174</v>
       </c>
       <c r="F17" s="14">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="G17" s="14">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="H17" s="15">
-        <v>-12.266666666666</v>
+        <v>-18.863049095607</v>
       </c>
       <c r="I17" s="14">
-        <v>1328</v>
+        <v>1417</v>
       </c>
       <c r="J17" s="14">
-        <v>1334</v>
+        <v>1443</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.449775112443</v>
+        <v>-1.801801801801</v>
       </c>
       <c r="L17" s="15">
-        <v>3.912363067292</v>
+        <v>3.279883381924</v>
       </c>
       <c r="M17" s="15">
-        <v>38.622129436325</v>
+        <v>38.514173998045</v>
       </c>
       <c r="N17" s="15">
-        <v>-45.662847790507</v>
+        <v>-45.833333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D18" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E18" s="15">
-        <v>-42.857142857142</v>
+        <v>-43.75</v>
       </c>
       <c r="F18" s="14">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G18" s="14">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H18" s="15">
-        <v>-38.211382113821</v>
+        <v>-40.151515151515</v>
       </c>
       <c r="I18" s="14">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="J18" s="14">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="K18" s="15">
-        <v>-5.598455598455</v>
+        <v>-7.454545454545</v>
       </c>
       <c r="L18" s="15">
-        <v>-17.676767676767</v>
+        <v>-20.344287949921</v>
       </c>
       <c r="M18" s="15">
-        <v>-40.073529411764</v>
+        <v>-41.561423650975</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.390203172836</v>
+        <v>-86.534391534391</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D19" s="14">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E19" s="15">
-        <v>-14.018691588785</v>
+        <v>2.884615384615</v>
       </c>
       <c r="F19" s="14">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="G19" s="14">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H19" s="15">
-        <v>0.493827160493</v>
+        <v>1.231527093596</v>
       </c>
       <c r="I19" s="14">
-        <v>1536</v>
+        <v>1647</v>
       </c>
       <c r="J19" s="14">
-        <v>1560</v>
+        <v>1664</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.538461538461</v>
+        <v>-1.021634615384</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.398537477148</v>
+        <v>-5.507745266781</v>
       </c>
       <c r="M19" s="15">
-        <v>31.058020477815</v>
+        <v>31.76</v>
       </c>
       <c r="N19" s="15">
-        <v>-19.454640797063</v>
+        <v>-19.658536585365</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D20" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E20" s="15">
-        <v>-14.705882352941</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F20" s="14">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G20" s="14">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H20" s="15">
-        <v>-19.047619047619</v>
+        <v>-21.323529411764</v>
       </c>
       <c r="I20" s="14">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="J20" s="14">
-        <v>404</v>
+        <v>442</v>
       </c>
       <c r="K20" s="15">
-        <v>-1.237623762376</v>
+        <v>-3.393665158371</v>
       </c>
       <c r="L20" s="15">
-        <v>-18.404907975460</v>
+        <v>-17.884615384615</v>
       </c>
       <c r="M20" s="15">
-        <v>-3.155339805825</v>
+        <v>-1.157407407407</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.345385347288</v>
+        <v>-87.095799335146</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="D21" s="17">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.268656716417</v>
+        <v>-18.713450292397</v>
       </c>
       <c r="F21" s="17">
-        <v>1063</v>
+        <v>1073</v>
       </c>
       <c r="G21" s="17">
-        <v>1195</v>
+        <v>1233</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.046025104602</v>
+        <v>-12.976480129764</v>
       </c>
       <c r="I21" s="17">
-        <v>4443</v>
+        <v>4733</v>
       </c>
       <c r="J21" s="17">
-        <v>4463</v>
+        <v>4805</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.448129061169</v>
+        <v>-1.498439125910</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.316137020222</v>
+        <v>-8.576395595904</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.089948279739</v>
+        <v>-0.252897787144</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.064565019702</v>
+        <v>-72.960466179159</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="14">
+        <v>4</v>
+      </c>
+      <c r="D22" s="14">
+        <v>7</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="F22" s="14">
+        <v>28</v>
+      </c>
+      <c r="G22" s="14">
+        <v>26</v>
+      </c>
+      <c r="H22" s="15">
+        <v>7.692307692307</v>
+      </c>
+      <c r="I22" s="14">
+        <v>110</v>
+      </c>
+      <c r="J22" s="14">
+        <v>105</v>
+      </c>
+      <c r="K22" s="15">
+        <v>4.761904761904</v>
+      </c>
+      <c r="L22" s="15">
+        <v>7.843137254901</v>
+      </c>
+      <c r="M22" s="15">
+        <v>-19.117647058823</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C22" s="14">
-        <v>3</v>
-      </c>
-      <c r="D22" s="14">
-        <v>8</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-62.5</v>
-      </c>
-      <c r="F22" s="14">
-        <v>33</v>
-      </c>
-      <c r="G22" s="14">
-        <v>22</v>
-      </c>
-      <c r="H22" s="15">
-        <v>50</v>
-      </c>
-      <c r="I22" s="14">
-        <v>106</v>
-      </c>
-      <c r="J22" s="14">
-        <v>98</v>
-      </c>
-      <c r="K22" s="15">
-        <v>8.163265306122</v>
-      </c>
-      <c r="L22" s="15">
-        <v>9.278350515463</v>
-      </c>
-      <c r="M22" s="15">
-        <v>-19.083969465648</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D23" s="14">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E23" s="15">
-        <v>-22.580645161290</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="F23" s="14">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G23" s="14">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H23" s="15">
-        <v>-21.238938053097</v>
+        <v>-19.166666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="J23" s="14">
-        <v>442</v>
+        <v>483</v>
       </c>
       <c r="K23" s="15">
-        <v>-7.466063348416</v>
+        <v>-9.316770186335</v>
       </c>
       <c r="L23" s="15">
-        <v>-13.713080168776</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M23" s="15">
-        <v>36.333333333333</v>
+        <v>36.448598130841</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D24" s="14">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="E24" s="15">
-        <v>4.932735426008</v>
+        <v>-12.267657992565</v>
       </c>
       <c r="F24" s="14">
-        <v>923</v>
+        <v>936</v>
       </c>
       <c r="G24" s="14">
-        <v>956</v>
+        <v>987</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.451882845188</v>
+        <v>-5.167173252279</v>
       </c>
       <c r="I24" s="14">
-        <v>3614</v>
+        <v>3849</v>
       </c>
       <c r="J24" s="14">
-        <v>3658</v>
+        <v>3927</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.202843083652</v>
+        <v>-1.986249045072</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.652359370834</v>
+        <v>-3.388554216867</v>
       </c>
       <c r="M24" s="15">
-        <v>24.277854195323</v>
+        <v>24.161290322580</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D25" s="14">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E25" s="15">
-        <v>-14.736842105263</v>
+        <v>-21.495327102803</v>
       </c>
       <c r="F25" s="14">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="G25" s="14">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="H25" s="15">
-        <v>-13.896457765667</v>
+        <v>-16.030534351145</v>
       </c>
       <c r="I25" s="14">
-        <v>1280</v>
+        <v>1364</v>
       </c>
       <c r="J25" s="14">
-        <v>1454</v>
+        <v>1561</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.966987620357</v>
+        <v>-12.620115310698</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.353293413173</v>
+        <v>-23.111612175873</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D26" s="14">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="E26" s="15">
-        <v>-20.496894409937</v>
+        <v>6.818181818181</v>
       </c>
       <c r="F26" s="14">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="G26" s="14">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="H26" s="15">
-        <v>0.787401574803</v>
+        <v>0.194174757281</v>
       </c>
       <c r="I26" s="14">
-        <v>1910</v>
+        <v>2045</v>
       </c>
       <c r="J26" s="14">
-        <v>1831</v>
+        <v>1963</v>
       </c>
       <c r="K26" s="15">
-        <v>4.314582195521</v>
+        <v>4.177279673968</v>
       </c>
       <c r="L26" s="15">
-        <v>1.272534464475</v>
+        <v>2.557673019057</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.484477481416</v>
+        <v>-17.373737373737</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1388,37 +1388,37 @@
         <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27" s="15">
-        <v>-60</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F27" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G27" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H27" s="15">
-        <v>-14.285714285714</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I27" s="14">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J27" s="14">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K27" s="15">
-        <v>19.191919191919</v>
+        <v>13.207547169811</v>
       </c>
       <c r="L27" s="15">
-        <v>6.306306306306</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D28" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E28" s="15">
-        <v>-11.764705882352</v>
+        <v>5</v>
       </c>
       <c r="F28" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G28" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H28" s="15">
-        <v>1.612903225806</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="I28" s="14">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="J28" s="14">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="K28" s="15">
-        <v>-4.761904761904</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="L28" s="15">
-        <v>14.285714285714</v>
+        <v>14.361702127659</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="F29" s="14">
+        <v>11</v>
+      </c>
+      <c r="G29" s="14">
+        <v>17</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-35.294117647058</v>
+      </c>
+      <c r="I29" s="14">
+        <v>49</v>
+      </c>
+      <c r="J29" s="14">
+        <v>61</v>
+      </c>
+      <c r="K29" s="15">
+        <v>-19.672131147541</v>
+      </c>
+      <c r="L29" s="15">
+        <v>-14.035087719298</v>
+      </c>
+      <c r="M29" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="F29" s="14">
-        <v>13</v>
-      </c>
-      <c r="G29" s="14">
-        <v>15</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-13.333333333333</v>
-      </c>
-      <c r="I29" s="14">
-        <v>45</v>
-      </c>
-      <c r="J29" s="14">
-        <v>54</v>
-      </c>
-      <c r="K29" s="15">
-        <v>-16.666666666666</v>
-      </c>
-      <c r="L29" s="15">
-        <v>-11.764705882352</v>
-      </c>
-      <c r="M29" s="15">
-        <v>-67.391304347826</v>
-      </c>
       <c r="N29" s="15">
-        <v>-92.320819112628</v>
+        <v>-92.185007974481</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,81 +1508,81 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="F30" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G30" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H30" s="15">
-        <v>-9.090909090909</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I30" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J30" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K30" s="15">
-        <v>-15.555555555555</v>
+        <v>-18</v>
       </c>
       <c r="L30" s="15">
-        <v>-17.391304347826</v>
+        <v>-19.607843137254</v>
       </c>
       <c r="M30" s="15">
-        <v>-63.106796116504</v>
+        <v>-63.063063063063</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.923649906890</v>
+        <v>-92.832167832167</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>4</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" s="15">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G31" s="14">
         <v>16</v>
       </c>
       <c r="H31" s="15">
-        <v>-62.5</v>
+        <v>-56.25</v>
       </c>
       <c r="I31" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J31" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K31" s="15">
-        <v>-17.857142857142</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="L31" s="15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,41 +1607,41 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J33" s="14">
         <v>8</v>
       </c>
       <c r="K33" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>708</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>20509</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>9978</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>14993</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>8788</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>12552</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>68033</v>

--- a/data/source/weekly/cs-en-us-pbbn.xlsx
+++ b/data/source/weekly/cs-en-us-pbbn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -851,369 +851,369 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14">
+        <v>2</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>4</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I14" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J14" s="14">
         <v>21</v>
       </c>
       <c r="K14" s="15">
-        <v>-42.857142857142</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="L14" s="15">
-        <v>-52</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M14" s="15">
-        <v>-69.230769230769</v>
+        <v>-60.975609756097</v>
       </c>
       <c r="N14" s="15">
-        <v>-92.105263157894</v>
+        <v>-90.123456790123</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>-71.428571428571</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H15" s="15">
-        <v>-31.578947368421</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I15" s="14">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J15" s="14">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K15" s="15">
-        <v>24.390243902439</v>
+        <v>24.418604651162</v>
       </c>
       <c r="L15" s="15">
-        <v>30.769230769230</v>
+        <v>30.487804878048</v>
       </c>
       <c r="M15" s="15">
-        <v>32.467532467532</v>
+        <v>30.487804878048</v>
       </c>
       <c r="N15" s="15">
-        <v>-49.753694581280</v>
+        <v>-51.141552511415</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D16" s="14">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E16" s="15">
-        <v>-25.490196078431</v>
+        <v>-27.868852459016</v>
       </c>
       <c r="F16" s="14">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="G16" s="14">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="H16" s="15">
-        <v>-3.973509933774</v>
+        <v>-12.568306010929</v>
       </c>
       <c r="I16" s="14">
-        <v>619</v>
+        <v>667</v>
       </c>
       <c r="J16" s="14">
-        <v>603</v>
+        <v>664</v>
       </c>
       <c r="K16" s="15">
-        <v>2.653399668325</v>
+        <v>0.451807228915</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.625</v>
+        <v>-22.261072261072</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.215574548907</v>
+        <v>-40.868794326241</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.524286243974</v>
+        <v>-88.316692940970</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D17" s="14">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="E17" s="15">
-        <v>-23.853211009174</v>
+        <v>-2.247191011235</v>
       </c>
       <c r="F17" s="14">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="G17" s="14">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="H17" s="15">
-        <v>-18.863049095607</v>
+        <v>-20</v>
       </c>
       <c r="I17" s="14">
-        <v>1417</v>
+        <v>1514</v>
       </c>
       <c r="J17" s="14">
-        <v>1443</v>
+        <v>1532</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.801801801801</v>
+        <v>-1.174934725848</v>
       </c>
       <c r="L17" s="15">
-        <v>3.279883381924</v>
+        <v>3.556771545827</v>
       </c>
       <c r="M17" s="15">
-        <v>38.514173998045</v>
+        <v>39.796860572483</v>
       </c>
       <c r="N17" s="15">
-        <v>-45.833333333333</v>
+        <v>-46.369110874955</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="14">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>24</v>
       </c>
-      <c r="C18" s="14">
-        <v>18</v>
-      </c>
-      <c r="D18" s="14">
-        <v>32</v>
-      </c>
       <c r="E18" s="15">
-        <v>-43.75</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G18" s="14">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H18" s="15">
-        <v>-40.151515151515</v>
+        <v>-41.538461538461</v>
       </c>
       <c r="I18" s="14">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="J18" s="14">
-        <v>550</v>
+        <v>574</v>
       </c>
       <c r="K18" s="15">
-        <v>-7.454545454545</v>
+        <v>-7.491289198606</v>
       </c>
       <c r="L18" s="15">
-        <v>-20.344287949921</v>
+        <v>-21.565731166912</v>
       </c>
       <c r="M18" s="15">
-        <v>-41.561423650975</v>
+        <v>-43.570669500531</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.534391534391</v>
+        <v>-86.698396793587</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D19" s="14">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="E19" s="15">
-        <v>2.884615384615</v>
+        <v>-14.925373134328</v>
       </c>
       <c r="F19" s="14">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="G19" s="14">
-        <v>406</v>
+        <v>444</v>
       </c>
       <c r="H19" s="15">
-        <v>1.231527093596</v>
+        <v>-5.630630630630</v>
       </c>
       <c r="I19" s="14">
-        <v>1647</v>
+        <v>1767</v>
       </c>
       <c r="J19" s="14">
-        <v>1664</v>
+        <v>1798</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.021634615384</v>
+        <v>-1.724137931034</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.507745266781</v>
+        <v>-3.600654664484</v>
       </c>
       <c r="M19" s="15">
-        <v>31.76</v>
+        <v>33.863636363636</v>
       </c>
       <c r="N19" s="15">
-        <v>-19.658536585365</v>
+        <v>-18.421052631578</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D20" s="14">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E20" s="15">
-        <v>-21.052631578947</v>
+        <v>-5</v>
       </c>
       <c r="F20" s="14">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G20" s="14">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H20" s="15">
-        <v>-21.323529411764</v>
+        <v>-20.161290322580</v>
       </c>
       <c r="I20" s="14">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="J20" s="14">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.393665158371</v>
+        <v>-4.329004329004</v>
       </c>
       <c r="L20" s="15">
-        <v>-17.884615384615</v>
+        <v>-21.492007104795</v>
       </c>
       <c r="M20" s="15">
-        <v>-1.157407407407</v>
+        <v>-4.329004329004</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.095799335146</v>
+        <v>-87.221740387395</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="D21" s="17">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.713450292397</v>
+        <v>-12.650602409638</v>
       </c>
       <c r="F21" s="17">
-        <v>1073</v>
+        <v>1100</v>
       </c>
       <c r="G21" s="17">
-        <v>1233</v>
+        <v>1314</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.976480129764</v>
+        <v>-16.286149162861</v>
       </c>
       <c r="I21" s="17">
-        <v>4733</v>
+        <v>5044</v>
       </c>
       <c r="J21" s="17">
-        <v>4805</v>
+        <v>5137</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.498439125910</v>
+        <v>-1.810395172279</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.576395595904</v>
+        <v>-8.307580439920</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.252897787144</v>
+        <v>-0.257069408740</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.960466179159</v>
+        <v>-72.779276848354</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D22" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>-42.857142857142</v>
+        <v>400</v>
       </c>
       <c r="F22" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G22" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H22" s="15">
-        <v>7.692307692307</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I22" s="14">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J22" s="14">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K22" s="15">
-        <v>4.761904761904</v>
+        <v>14.018691588785</v>
       </c>
       <c r="L22" s="15">
-        <v>7.843137254901</v>
+        <v>15.094339622641</v>
       </c>
       <c r="M22" s="15">
-        <v>-19.117647058823</v>
+        <v>-14.685314685314</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D23" s="14">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E23" s="15">
-        <v>-34.146341463414</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="F23" s="14">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G23" s="14">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="H23" s="15">
-        <v>-19.166666666666</v>
+        <v>-26.865671641791</v>
       </c>
       <c r="I23" s="14">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="J23" s="14">
-        <v>483</v>
+        <v>518</v>
       </c>
       <c r="K23" s="15">
-        <v>-9.316770186335</v>
+        <v>-10.231660231660</v>
       </c>
       <c r="L23" s="15">
-        <v>-14.285714285714</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="M23" s="15">
-        <v>36.448598130841</v>
+        <v>32.478632478632</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D24" s="14">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="E24" s="15">
-        <v>-12.267657992565</v>
+        <v>-17.753623188405</v>
       </c>
       <c r="F24" s="14">
-        <v>936</v>
+        <v>903</v>
       </c>
       <c r="G24" s="14">
-        <v>987</v>
+        <v>1019</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.167173252279</v>
+        <v>-11.383709519136</v>
       </c>
       <c r="I24" s="14">
-        <v>3849</v>
+        <v>4075</v>
       </c>
       <c r="J24" s="14">
-        <v>3927</v>
+        <v>4203</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.986249045072</v>
+        <v>-3.045443730668</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.388554216867</v>
+        <v>-3.298528713811</v>
       </c>
       <c r="M24" s="15">
-        <v>24.161290322580</v>
+        <v>23.822546338498</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D25" s="14">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E25" s="15">
-        <v>-21.495327102803</v>
+        <v>-37.5</v>
       </c>
       <c r="F25" s="14">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="G25" s="14">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="H25" s="15">
-        <v>-16.030534351145</v>
+        <v>-24.396135265700</v>
       </c>
       <c r="I25" s="14">
-        <v>1364</v>
+        <v>1435</v>
       </c>
       <c r="J25" s="14">
-        <v>1561</v>
+        <v>1673</v>
       </c>
       <c r="K25" s="15">
-        <v>-12.620115310698</v>
+        <v>-14.225941422594</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.111612175873</v>
+        <v>-23.425827107790</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D26" s="14">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E26" s="15">
-        <v>6.818181818181</v>
+        <v>-2.189781021897</v>
       </c>
       <c r="F26" s="14">
-        <v>516</v>
+        <v>543</v>
       </c>
       <c r="G26" s="14">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="H26" s="15">
-        <v>0.194174757281</v>
+        <v>2.840909090909</v>
       </c>
       <c r="I26" s="14">
-        <v>2045</v>
+        <v>2175</v>
       </c>
       <c r="J26" s="14">
-        <v>1963</v>
+        <v>2100</v>
       </c>
       <c r="K26" s="15">
-        <v>4.177279673968</v>
+        <v>3.571428571428</v>
       </c>
       <c r="L26" s="15">
-        <v>2.557673019057</v>
+        <v>2.208646616541</v>
       </c>
       <c r="M26" s="15">
-        <v>-17.373737373737</v>
+        <v>-18.079096045197</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E27" s="15">
-        <v>-71.428571428571</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>17</v>
       </c>
       <c r="G27" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H27" s="15">
-        <v>-22.727272727272</v>
+        <v>-32</v>
       </c>
       <c r="I27" s="14">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J27" s="14">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="K27" s="15">
-        <v>13.207547169811</v>
+        <v>12.612612612612</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-0.793650793650</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>16</v>
+      </c>
+      <c r="D28" s="14">
+        <v>10</v>
+      </c>
+      <c r="E28" s="15">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>69</v>
+      </c>
+      <c r="G28" s="14">
+        <v>60</v>
+      </c>
+      <c r="H28" s="15">
+        <v>15</v>
+      </c>
+      <c r="I28" s="14">
+        <v>231</v>
+      </c>
+      <c r="J28" s="14">
+        <v>240</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-3.75</v>
+      </c>
+      <c r="L28" s="15">
+        <v>15.5</v>
+      </c>
+      <c r="M28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="14">
-        <v>20</v>
-      </c>
-      <c r="E28" s="15">
-        <v>5</v>
-      </c>
-      <c r="F28" s="14">
-        <v>64</v>
-      </c>
-      <c r="G28" s="14">
-        <v>66</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-3.030303030303</v>
-      </c>
-      <c r="I28" s="14">
-        <v>215</v>
-      </c>
-      <c r="J28" s="14">
-        <v>230</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-6.521739130434</v>
-      </c>
-      <c r="L28" s="15">
-        <v>14.361702127659</v>
-      </c>
-      <c r="M28" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>-42.857142857142</v>
+        <v>100</v>
       </c>
       <c r="F29" s="14">
         <v>11</v>
       </c>
       <c r="G29" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H29" s="15">
-        <v>-35.294117647058</v>
+        <v>-31.25</v>
       </c>
       <c r="I29" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J29" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K29" s="15">
-        <v>-19.672131147541</v>
+        <v>-17.741935483871</v>
       </c>
       <c r="L29" s="15">
-        <v>-14.035087719298</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-66</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.185007974481</v>
+        <v>-92.477876106194</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,40 +1508,40 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>-40</v>
+        <v>100</v>
       </c>
       <c r="F30" s="14">
         <v>9</v>
       </c>
       <c r="G30" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H30" s="15">
-        <v>-30.769230769230</v>
+        <v>-25</v>
       </c>
       <c r="I30" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J30" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K30" s="15">
-        <v>-18</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="L30" s="15">
-        <v>-19.607843137254</v>
+        <v>-23.214285714285</v>
       </c>
       <c r="M30" s="15">
-        <v>-63.063063063063</v>
+        <v>-62.280701754386</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.832167832167</v>
+        <v>-93.053311793214</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,37 +1552,37 @@
         <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="15">
         <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G31" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H31" s="15">
-        <v>-56.25</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I31" s="14">
         <v>24</v>
       </c>
       <c r="J31" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K31" s="15">
-        <v>-22.580645161290</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="L31" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,34 +1614,34 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I33" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J33" s="14">
         <v>8</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="L33" s="15">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>708</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>20509</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>9978</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>14993</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>8788</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>12552</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>68033</v>
